--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -1178,16 +1178,16 @@
     <t>2026-01-01T10:16:00.000Z</t>
   </si>
   <si>
-    <t>unmarked_lost</t>
-  </si>
-  <si>
-    <t>נמצא בחיפוש בציוד</t>
+    <t>found_returned</t>
+  </si>
+  <si>
+    <t>ציוד אבוד נמצא והוחזר למחסן</t>
   </si>
   <si>
     <t>2026-01-01T10:17:00.000Z</t>
   </si>
   <si>
-    <t>הוחזר תקין לאחר איתור</t>
+    <t>החזרה רגילה של היחידה שנותרה בהשאלה</t>
   </si>
   <si>
     <t>2026-01-01T10:18:00.000Z</t>
@@ -1939,7 +1939,7 @@
   </sheetData>
   <autoFilter ref="A1:B1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3717,7 +3717,7 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3764,7 +3764,7 @@
   </sheetData>
   <autoFilter ref="A1:B1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5982,7 +5982,7 @@
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6257,7 +6257,7 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -9104,7 +9104,7 @@
         <v>178</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139">
         <v>135</v>
@@ -9876,7 +9876,7 @@
         <v>178</v>
       </c>
       <c r="E171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F171">
         <v>167</v>
@@ -10648,7 +10648,7 @@
         <v>178</v>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F203">
         <v>199</v>
@@ -11118,7 +11118,7 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -11232,7 +11232,7 @@
   </sheetData>
   <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -12101,6 +12101,6 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="798">
   <si>
     <t>Name</t>
   </si>
@@ -917,7 +917,7 @@
     <t>קליטת מלאי נוסף</t>
   </si>
   <si>
-    <t>2026-01-01T09:13:00.000Z</t>
+    <t>2026-01-02T08:05:00.000Z</t>
   </si>
   <si>
     <t>issued</t>
@@ -926,19 +926,19 @@
     <t>נופק לצוותי העבודה</t>
   </si>
   <si>
-    <t>2026-01-01T09:14:00.000Z</t>
+    <t>2026-01-02T08:17:00.000Z</t>
   </si>
   <si>
     <t>השלמת מלאי</t>
   </si>
   <si>
-    <t>2026-01-01T09:15:00.000Z</t>
+    <t>2026-01-02T08:29:00.000Z</t>
   </si>
   <si>
     <t>נופק להקמות בשטח</t>
   </si>
   <si>
-    <t>2026-01-01T09:16:00.000Z</t>
+    <t>2026-01-02T08:41:00.000Z</t>
   </si>
   <si>
     <t>stock_removed</t>
@@ -947,166 +947,166 @@
     <t>תיקון ספירה לאחר בדיקת מדף</t>
   </si>
   <si>
-    <t>2026-01-01T09:17:00.000Z</t>
+    <t>2026-01-02T08:53:00.000Z</t>
   </si>
   <si>
     <t>הפחתה בעקבות בלאי או אריזה פגומה</t>
   </si>
   <si>
-    <t>2026-01-01T09:18:00.000Z</t>
+    <t>2026-01-02T09:05:00.000Z</t>
   </si>
   <si>
     <t>קליטת אספקה</t>
   </si>
   <si>
-    <t>2026-01-01T09:19:00.000Z</t>
+    <t>2026-01-02T09:17:00.000Z</t>
   </si>
   <si>
     <t>נופק לפעילות בשטח</t>
   </si>
   <si>
-    <t>2026-01-01T09:20:00.000Z</t>
+    <t>2026-01-02T09:29:00.000Z</t>
   </si>
   <si>
     <t>תיקון ספירת מלאי</t>
   </si>
   <si>
-    <t>2026-01-01T09:21:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:22:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:23:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:24:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:25:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:26:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:27:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:28:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:29:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:30:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:31:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:32:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:33:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:34:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:35:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:36:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:37:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:38:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:39:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:40:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:41:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:42:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:43:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:44:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:45:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:46:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:47:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:48:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:49:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:50:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:51:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:52:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:53:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:54:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:55:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:56:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:57:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:58:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T09:59:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:01:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:02:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:03:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:04:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:05:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:06:00.000Z</t>
+    <t>2026-01-02T09:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T09:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T10:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T10:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T10:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T10:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T10:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T11:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T11:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T11:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T11:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T11:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T12:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T12:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T12:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T12:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T12:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T13:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T13:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T13:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T13:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-02T13:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T08:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T08:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T08:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T08:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T08:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T09:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T09:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T09:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T09:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T09:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T10:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T10:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T10:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T10:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T10:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T11:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T11:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T11:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T11:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T11:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T12:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T12:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T12:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-03T12:41:00.000Z</t>
   </si>
   <si>
     <t>checked_out</t>
@@ -1115,13 +1115,13 @@
     <t>השאלה פעילה בשטח</t>
   </si>
   <si>
-    <t>2026-01-01T10:07:00.000Z</t>
+    <t>2026-01-03T12:53:00.000Z</t>
   </si>
   <si>
     <t>השאלה למחנה</t>
   </si>
   <si>
-    <t>2026-01-01T10:08:00.000Z</t>
+    <t>2026-01-03T13:05:00.000Z</t>
   </si>
   <si>
     <t>returned_usable</t>
@@ -1130,31 +1130,31 @@
     <t>החזרה חלקית תקינה</t>
   </si>
   <si>
-    <t>2026-01-01T10:09:00.000Z</t>
+    <t>2026-01-03T13:17:00.000Z</t>
   </si>
   <si>
     <t>השאלה להקמות</t>
   </si>
   <si>
-    <t>2026-01-01T10:10:00.000Z</t>
+    <t>2026-01-03T13:29:00.000Z</t>
   </si>
   <si>
     <t>החזרה חלקית: תקין ופגום</t>
   </si>
   <si>
-    <t>2026-01-01T10:11:00.000Z</t>
+    <t>2026-01-03T13:41:00.000Z</t>
   </si>
   <si>
     <t>returned_damaged</t>
   </si>
   <si>
-    <t>2026-01-01T10:12:00.000Z</t>
+    <t>2026-01-03T13:53:00.000Z</t>
   </si>
   <si>
     <t>השאלה לצוות בשטח</t>
   </si>
   <si>
-    <t>2026-01-01T10:13:00.000Z</t>
+    <t>2026-01-04T08:05:00.000Z</t>
   </si>
   <si>
     <t>marked_lost</t>
@@ -1163,19 +1163,19 @@
     <t>לא נמצא לאחר מעבר מחנה</t>
   </si>
   <si>
-    <t>2026-01-01T10:14:00.000Z</t>
+    <t>2026-01-04T08:17:00.000Z</t>
   </si>
   <si>
     <t>השאלה היסטורית</t>
   </si>
   <si>
-    <t>2026-01-01T10:15:00.000Z</t>
+    <t>2026-01-04T08:29:00.000Z</t>
   </si>
   <si>
     <t>סומן כאבוד זמנית</t>
   </si>
   <si>
-    <t>2026-01-01T10:16:00.000Z</t>
+    <t>2026-01-04T08:41:00.000Z</t>
   </si>
   <si>
     <t>found_returned</t>
@@ -1184,28 +1184,28 @@
     <t>ציוד אבוד נמצא והוחזר למחסן</t>
   </si>
   <si>
-    <t>2026-01-01T10:17:00.000Z</t>
+    <t>2026-01-04T08:53:00.000Z</t>
   </si>
   <si>
     <t>החזרה רגילה של היחידה שנותרה בהשאלה</t>
   </si>
   <si>
-    <t>2026-01-01T10:18:00.000Z</t>
+    <t>2026-01-04T09:05:00.000Z</t>
   </si>
   <si>
     <t>השאלה לעבודות שטח</t>
   </si>
   <si>
-    <t>2026-01-01T10:19:00.000Z</t>
+    <t>2026-01-04T09:17:00.000Z</t>
   </si>
   <si>
     <t>הוחזר עם נזק</t>
   </si>
   <si>
-    <t>2026-01-01T10:20:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:21:00.000Z</t>
+    <t>2026-01-04T09:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T09:41:00.000Z</t>
   </si>
   <si>
     <t>repaired</t>
@@ -1214,19 +1214,19 @@
     <t>יחידה אחת תוקנה; אחת ממתינה לטיפול</t>
   </si>
   <si>
-    <t>2026-01-01T10:22:00.000Z</t>
+    <t>2026-01-04T09:53:00.000Z</t>
   </si>
   <si>
     <t>השאלה שהסתיימה</t>
   </si>
   <si>
-    <t>2026-01-01T10:23:00.000Z</t>
+    <t>2026-01-04T10:05:00.000Z</t>
   </si>
   <si>
     <t>שתי יחידות הוחזרו פגומות</t>
   </si>
   <si>
-    <t>2026-01-01T10:24:00.000Z</t>
+    <t>2026-01-04T10:17:00.000Z</t>
   </si>
   <si>
     <t>written_off</t>
@@ -1235,271 +1235,1165 @@
     <t>הוצאה מהמלאי לאחר בדיקה</t>
   </si>
   <si>
-    <t>2026-01-01T10:25:00.000Z</t>
+    <t>2026-01-04T10:29:00.000Z</t>
   </si>
   <si>
     <t>השאלה קצרה שהסתיימה</t>
   </si>
   <si>
-    <t>2026-01-01T10:26:00.000Z</t>
+    <t>2026-01-04T10:41:00.000Z</t>
   </si>
   <si>
     <t>הוחזר במלואו</t>
   </si>
   <si>
-    <t>2026-01-01T10:27:00.000Z</t>
+    <t>2026-01-04T10:53:00.000Z</t>
   </si>
   <si>
     <t>השאלה נוספת שעדיין פעילה</t>
   </si>
   <si>
-    <t>2026-01-01T10:28:00.000Z</t>
+    <t>2026-01-04T11:05:00.000Z</t>
   </si>
   <si>
     <t>השאלה שגרתית</t>
   </si>
   <si>
-    <t>2026-01-01T10:29:00.000Z</t>
+    <t>2026-01-04T11:17:00.000Z</t>
   </si>
   <si>
     <t>הוחזר מלא ותקין</t>
   </si>
   <si>
-    <t>2026-01-01T10:30:00.000Z</t>
+    <t>2026-01-04T11:29:00.000Z</t>
   </si>
   <si>
     <t>השאלה גדולה עם סטטוסים מעורבים</t>
   </si>
   <si>
-    <t>2026-01-01T10:31:00.000Z</t>
+    <t>2026-01-04T11:41:00.000Z</t>
   </si>
   <si>
     <t>החזרה חלקית</t>
   </si>
   <si>
-    <t>2026-01-01T10:32:00.000Z</t>
+    <t>2026-01-04T11:53:00.000Z</t>
   </si>
   <si>
     <t>יחידה אחת חסרה; שתיים עדיין בשטח</t>
   </si>
   <si>
-    <t>2026-01-01T10:33:00.000Z</t>
+    <t>2026-01-04T12:05:00.000Z</t>
   </si>
   <si>
     <t>השאלה לפני סבב תחזוקה</t>
   </si>
   <si>
-    <t>2026-01-01T10:34:00.000Z</t>
+    <t>2026-01-04T12:17:00.000Z</t>
   </si>
   <si>
     <t>שתיים תקינות ושתיים פגומות</t>
   </si>
   <si>
-    <t>2026-01-01T10:35:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:36:00.000Z</t>
+    <t>2026-01-04T12:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T12:41:00.000Z</t>
   </si>
   <si>
     <t>שתי היחידות הפגומות תוקנו</t>
   </si>
   <si>
-    <t>2026-01-01T10:37:00.000Z</t>
+    <t>2026-01-04T12:53:00.000Z</t>
   </si>
   <si>
     <t>נקלטה יחידת ציוד נוספת</t>
   </si>
   <si>
-    <t>2026-01-01T10:38:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:39:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:40:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:41:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:42:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:43:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:44:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:45:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:46:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:47:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:48:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:49:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:50:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:51:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:52:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:53:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:54:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:55:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:56:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:57:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:58:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T10:59:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:01:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:02:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:03:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:04:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:05:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:06:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:07:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:08:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:09:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:10:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:11:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:12:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:13:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:14:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:15:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:16:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:17:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:18:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:19:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:20:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:21:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:22:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:23:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:24:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:25:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:26:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:27:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:28:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:29:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:30:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:31:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:32:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:33:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:34:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:35:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:36:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:37:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:38:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:39:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:40:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-01-01T11:41:00.000Z</t>
+    <t>2026-01-04T13:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T13:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T13:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T13:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-04T13:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T08:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T08:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T08:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T08:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T08:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T10:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T10:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T10:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T10:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T10:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T11:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T11:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T11:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T11:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T11:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T12:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T12:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T12:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T12:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T12:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T13:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T13:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T13:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T13:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-05T13:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T08:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T08:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T08:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T08:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T08:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T09:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T09:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T09:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T09:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T09:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T10:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T10:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T10:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T10:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T10:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T11:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T11:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T11:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T11:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T11:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T12:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T12:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T12:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T12:41:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T12:53:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T13:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T13:17:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T13:29:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-06T13:41:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור הכנת שטח והקמת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-07T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור הכנת שטח והקמת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-07T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור הכנת שטח והקמת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-07T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-07T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר פריסת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-08T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור פריסת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-08T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור פריסת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-08T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור פריסת תשתיות</t>
+  </si>
+  <si>
+    <t>2026-01-08T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-08T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>התאמת מלאי לאחר ספירה במחסן</t>
+  </si>
+  <si>
+    <t>2026-01-08T14:46:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר פגום לאחר הרכבת מבנים</t>
+  </si>
+  <si>
+    <t>2026-01-09T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר הרכבת מבנים</t>
+  </si>
+  <si>
+    <t>2026-01-09T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור הרכבת מבנים</t>
+  </si>
+  <si>
+    <t>2026-01-09T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור הרכבת מבנים</t>
+  </si>
+  <si>
+    <t>2026-01-09T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור הרכבת מבנים</t>
+  </si>
+  <si>
+    <t>2026-01-09T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-09T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר התקנת חשמל ומים</t>
+  </si>
+  <si>
+    <t>2026-01-10T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>תוקן בבדיקת מחסן והוחזר לשימוש</t>
+  </si>
+  <si>
+    <t>2026-01-10T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור התקנת חשמל ומים</t>
+  </si>
+  <si>
+    <t>2026-01-10T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור התקנת חשמל ומים</t>
+  </si>
+  <si>
+    <t>2026-01-10T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור התקנת חשמל ומים</t>
+  </si>
+  <si>
+    <t>2026-01-10T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T14:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-10T14:58:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר המשך עבודות הקמה</t>
+  </si>
+  <si>
+    <t>2026-01-11T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור המשך עבודות הקמה</t>
+  </si>
+  <si>
+    <t>2026-01-11T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור המשך עבודות הקמה</t>
+  </si>
+  <si>
+    <t>2026-01-11T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור המשך עבודות הקמה</t>
+  </si>
+  <si>
+    <t>2026-01-11T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-11T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר פגום לאחר גמר ובדיקות בטיחות</t>
+  </si>
+  <si>
+    <t>2026-01-12T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר גמר ובדיקות בטיחות</t>
+  </si>
+  <si>
+    <t>2026-01-12T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור גמר ובדיקות בטיחות</t>
+  </si>
+  <si>
+    <t>2026-01-12T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור גמר ובדיקות בטיחות</t>
+  </si>
+  <si>
+    <t>2026-01-12T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור גמר ובדיקות בטיחות</t>
+  </si>
+  <si>
+    <t>2026-01-12T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-12T14:46:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר תיקונים והשלמות</t>
+  </si>
+  <si>
+    <t>2026-01-13T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור תיקונים והשלמות</t>
+  </si>
+  <si>
+    <t>2026-01-13T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור תיקונים והשלמות</t>
+  </si>
+  <si>
+    <t>2026-01-13T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור תיקונים והשלמות</t>
+  </si>
+  <si>
+    <t>2026-01-13T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-13T14:46:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר פגום לאחר מסירה וסגירת עבודות</t>
+  </si>
+  <si>
+    <t>2026-01-14T08:10:00.000Z</t>
+  </si>
+  <si>
+    <t>הוחזר תקין לאחר מסירה וסגירת עבודות</t>
+  </si>
+  <si>
+    <t>2026-01-14T08:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T08:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T08:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T08:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T09:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T09:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T09:34:00.000Z</t>
+  </si>
+  <si>
+    <t>אספקה למחסן עבור מסירה וסגירת עבודות</t>
+  </si>
+  <si>
+    <t>2026-01-14T09:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T09:58:00.000Z</t>
+  </si>
+  <si>
+    <t>נופק לצוות עבור מסירה וסגירת עבודות</t>
+  </si>
+  <si>
+    <t>2026-01-14T10:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T10:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T10:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T10:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T10:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T11:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T11:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T11:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T11:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T11:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T12:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T12:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T12:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T12:46:00.000Z</t>
+  </si>
+  <si>
+    <t>השאלה לצוות עבור מסירה וסגירת עבודות</t>
+  </si>
+  <si>
+    <t>2026-01-14T12:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T13:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T13:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T13:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T13:46:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T13:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T14:10:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T14:22:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T14:34:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-01-14T14:46:00.000Z</t>
   </si>
   <si>
     <t>Item Name</t>
@@ -1997,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2023,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2049,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2075,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>150</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2098,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2124,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2150,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2176,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>165</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2199,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2225,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2251,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2277,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2300,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2326,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2352,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2378,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2401,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2453,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2479,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>205</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2502,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2528,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2554,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2580,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>182</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2603,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2629,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2655,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -2681,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>130</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -2704,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -2730,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -2756,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -2782,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>145</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -2805,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -2831,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -2883,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>122</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -2906,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3021,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3205,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3320,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -6263,14 +7157,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H484"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11113,6 +12010,5798 @@
       </c>
       <c r="H222" t="s">
         <v>493</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>224</v>
+      </c>
+      <c r="C223">
+        <v>100</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="G223" t="s">
+        <v>494</v>
+      </c>
+      <c r="H223" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>224</v>
+      </c>
+      <c r="C224">
+        <v>107</v>
+      </c>
+      <c r="E224">
+        <v>48</v>
+      </c>
+      <c r="G224" t="s">
+        <v>494</v>
+      </c>
+      <c r="H224" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>300</v>
+      </c>
+      <c r="C225">
+        <v>100</v>
+      </c>
+      <c r="E225">
+        <v>3</v>
+      </c>
+      <c r="G225" t="s">
+        <v>497</v>
+      </c>
+      <c r="H225" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>300</v>
+      </c>
+      <c r="C226">
+        <v>101</v>
+      </c>
+      <c r="E226">
+        <v>6</v>
+      </c>
+      <c r="G226" t="s">
+        <v>497</v>
+      </c>
+      <c r="H226" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>300</v>
+      </c>
+      <c r="C227">
+        <v>102</v>
+      </c>
+      <c r="E227">
+        <v>12</v>
+      </c>
+      <c r="G227" t="s">
+        <v>497</v>
+      </c>
+      <c r="H227" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>300</v>
+      </c>
+      <c r="C228">
+        <v>103</v>
+      </c>
+      <c r="E228">
+        <v>24</v>
+      </c>
+      <c r="G228" t="s">
+        <v>497</v>
+      </c>
+      <c r="H228" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>300</v>
+      </c>
+      <c r="C229">
+        <v>104</v>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
+      <c r="G229" t="s">
+        <v>497</v>
+      </c>
+      <c r="H229" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>300</v>
+      </c>
+      <c r="C230">
+        <v>105</v>
+      </c>
+      <c r="E230">
+        <v>6</v>
+      </c>
+      <c r="G230" t="s">
+        <v>497</v>
+      </c>
+      <c r="H230" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>300</v>
+      </c>
+      <c r="C231">
+        <v>106</v>
+      </c>
+      <c r="E231">
+        <v>12</v>
+      </c>
+      <c r="G231" t="s">
+        <v>497</v>
+      </c>
+      <c r="H231" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>300</v>
+      </c>
+      <c r="C232">
+        <v>107</v>
+      </c>
+      <c r="E232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>497</v>
+      </c>
+      <c r="H232" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>300</v>
+      </c>
+      <c r="C233">
+        <v>108</v>
+      </c>
+      <c r="E233">
+        <v>5</v>
+      </c>
+      <c r="G233" t="s">
+        <v>497</v>
+      </c>
+      <c r="H233" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>300</v>
+      </c>
+      <c r="C234">
+        <v>109</v>
+      </c>
+      <c r="E234">
+        <v>6</v>
+      </c>
+      <c r="G234" t="s">
+        <v>497</v>
+      </c>
+      <c r="H234" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>300</v>
+      </c>
+      <c r="C235">
+        <v>110</v>
+      </c>
+      <c r="E235">
+        <v>12</v>
+      </c>
+      <c r="G235" t="s">
+        <v>497</v>
+      </c>
+      <c r="H235" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>300</v>
+      </c>
+      <c r="C236">
+        <v>111</v>
+      </c>
+      <c r="E236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>497</v>
+      </c>
+      <c r="H236" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>300</v>
+      </c>
+      <c r="C237">
+        <v>112</v>
+      </c>
+      <c r="E237">
+        <v>3</v>
+      </c>
+      <c r="G237" t="s">
+        <v>497</v>
+      </c>
+      <c r="H237" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>300</v>
+      </c>
+      <c r="C238">
+        <v>113</v>
+      </c>
+      <c r="E238">
+        <v>6</v>
+      </c>
+      <c r="G238" t="s">
+        <v>497</v>
+      </c>
+      <c r="H238" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>363</v>
+      </c>
+      <c r="C239">
+        <v>200</v>
+      </c>
+      <c r="D239" t="s">
+        <v>204</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+      <c r="G239" t="s">
+        <v>512</v>
+      </c>
+      <c r="H239" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>363</v>
+      </c>
+      <c r="C240">
+        <v>201</v>
+      </c>
+      <c r="D240" t="s">
+        <v>211</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+      <c r="G240" t="s">
+        <v>512</v>
+      </c>
+      <c r="H240" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>363</v>
+      </c>
+      <c r="C241">
+        <v>202</v>
+      </c>
+      <c r="D241" t="s">
+        <v>215</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+      <c r="G241" t="s">
+        <v>512</v>
+      </c>
+      <c r="H241" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>363</v>
+      </c>
+      <c r="C242">
+        <v>203</v>
+      </c>
+      <c r="D242" t="s">
+        <v>169</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="G242" t="s">
+        <v>512</v>
+      </c>
+      <c r="H242" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>363</v>
+      </c>
+      <c r="C243">
+        <v>204</v>
+      </c>
+      <c r="D243" t="s">
+        <v>174</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+      <c r="G243" t="s">
+        <v>512</v>
+      </c>
+      <c r="H243" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>363</v>
+      </c>
+      <c r="C244">
+        <v>205</v>
+      </c>
+      <c r="D244" t="s">
+        <v>183</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+      <c r="G244" t="s">
+        <v>512</v>
+      </c>
+      <c r="H244" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>363</v>
+      </c>
+      <c r="C245">
+        <v>206</v>
+      </c>
+      <c r="D245" t="s">
+        <v>188</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+      <c r="G245" t="s">
+        <v>512</v>
+      </c>
+      <c r="H245" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>363</v>
+      </c>
+      <c r="C246">
+        <v>208</v>
+      </c>
+      <c r="D246" t="s">
+        <v>192</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="G246" t="s">
+        <v>512</v>
+      </c>
+      <c r="H246" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>363</v>
+      </c>
+      <c r="C247">
+        <v>210</v>
+      </c>
+      <c r="D247" t="s">
+        <v>196</v>
+      </c>
+      <c r="E247">
+        <v>1</v>
+      </c>
+      <c r="G247" t="s">
+        <v>512</v>
+      </c>
+      <c r="H247" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>368</v>
+      </c>
+      <c r="C248">
+        <v>200</v>
+      </c>
+      <c r="D248" t="s">
+        <v>204</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+      <c r="F248">
+        <v>238</v>
+      </c>
+      <c r="G248" t="s">
+        <v>522</v>
+      </c>
+      <c r="H248" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>368</v>
+      </c>
+      <c r="C249">
+        <v>201</v>
+      </c>
+      <c r="D249" t="s">
+        <v>211</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+      <c r="F249">
+        <v>239</v>
+      </c>
+      <c r="G249" t="s">
+        <v>522</v>
+      </c>
+      <c r="H249" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>368</v>
+      </c>
+      <c r="C250">
+        <v>202</v>
+      </c>
+      <c r="D250" t="s">
+        <v>215</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+      <c r="F250">
+        <v>240</v>
+      </c>
+      <c r="G250" t="s">
+        <v>522</v>
+      </c>
+      <c r="H250" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>368</v>
+      </c>
+      <c r="C251">
+        <v>203</v>
+      </c>
+      <c r="D251" t="s">
+        <v>169</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+      <c r="F251">
+        <v>241</v>
+      </c>
+      <c r="G251" t="s">
+        <v>522</v>
+      </c>
+      <c r="H251" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>368</v>
+      </c>
+      <c r="C252">
+        <v>204</v>
+      </c>
+      <c r="D252" t="s">
+        <v>174</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+      <c r="F252">
+        <v>242</v>
+      </c>
+      <c r="G252" t="s">
+        <v>522</v>
+      </c>
+      <c r="H252" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>368</v>
+      </c>
+      <c r="C253">
+        <v>205</v>
+      </c>
+      <c r="D253" t="s">
+        <v>183</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+      <c r="F253">
+        <v>243</v>
+      </c>
+      <c r="G253" t="s">
+        <v>522</v>
+      </c>
+      <c r="H253" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>368</v>
+      </c>
+      <c r="C254">
+        <v>206</v>
+      </c>
+      <c r="D254" t="s">
+        <v>188</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+      <c r="F254">
+        <v>244</v>
+      </c>
+      <c r="G254" t="s">
+        <v>522</v>
+      </c>
+      <c r="H254" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>368</v>
+      </c>
+      <c r="C255">
+        <v>208</v>
+      </c>
+      <c r="D255" t="s">
+        <v>192</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255">
+        <v>245</v>
+      </c>
+      <c r="G255" t="s">
+        <v>522</v>
+      </c>
+      <c r="H255" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>224</v>
+      </c>
+      <c r="C256">
+        <v>102</v>
+      </c>
+      <c r="E256">
+        <v>24</v>
+      </c>
+      <c r="G256" t="s">
+        <v>531</v>
+      </c>
+      <c r="H256" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>224</v>
+      </c>
+      <c r="C257">
+        <v>109</v>
+      </c>
+      <c r="E257">
+        <v>12</v>
+      </c>
+      <c r="G257" t="s">
+        <v>531</v>
+      </c>
+      <c r="H257" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>300</v>
+      </c>
+      <c r="C258">
+        <v>114</v>
+      </c>
+      <c r="E258">
+        <v>12</v>
+      </c>
+      <c r="G258" t="s">
+        <v>534</v>
+      </c>
+      <c r="H258" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>300</v>
+      </c>
+      <c r="C259">
+        <v>115</v>
+      </c>
+      <c r="E259">
+        <v>24</v>
+      </c>
+      <c r="G259" t="s">
+        <v>534</v>
+      </c>
+      <c r="H259" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>300</v>
+      </c>
+      <c r="C260">
+        <v>116</v>
+      </c>
+      <c r="E260">
+        <v>5</v>
+      </c>
+      <c r="G260" t="s">
+        <v>534</v>
+      </c>
+      <c r="H260" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>300</v>
+      </c>
+      <c r="C261">
+        <v>118</v>
+      </c>
+      <c r="E261">
+        <v>12</v>
+      </c>
+      <c r="G261" t="s">
+        <v>534</v>
+      </c>
+      <c r="H261" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>300</v>
+      </c>
+      <c r="C262">
+        <v>119</v>
+      </c>
+      <c r="E262">
+        <v>24</v>
+      </c>
+      <c r="G262" t="s">
+        <v>534</v>
+      </c>
+      <c r="H262" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>300</v>
+      </c>
+      <c r="C263">
+        <v>120</v>
+      </c>
+      <c r="E263">
+        <v>5</v>
+      </c>
+      <c r="G263" t="s">
+        <v>534</v>
+      </c>
+      <c r="H263" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>300</v>
+      </c>
+      <c r="C264">
+        <v>121</v>
+      </c>
+      <c r="E264">
+        <v>6</v>
+      </c>
+      <c r="G264" t="s">
+        <v>534</v>
+      </c>
+      <c r="H264" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>300</v>
+      </c>
+      <c r="C265">
+        <v>122</v>
+      </c>
+      <c r="E265">
+        <v>12</v>
+      </c>
+      <c r="G265" t="s">
+        <v>534</v>
+      </c>
+      <c r="H265" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>300</v>
+      </c>
+      <c r="C266">
+        <v>123</v>
+      </c>
+      <c r="E266">
+        <v>24</v>
+      </c>
+      <c r="G266" t="s">
+        <v>534</v>
+      </c>
+      <c r="H266" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>300</v>
+      </c>
+      <c r="C267">
+        <v>124</v>
+      </c>
+      <c r="E267">
+        <v>3</v>
+      </c>
+      <c r="G267" t="s">
+        <v>534</v>
+      </c>
+      <c r="H267" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>300</v>
+      </c>
+      <c r="C268">
+        <v>125</v>
+      </c>
+      <c r="E268">
+        <v>6</v>
+      </c>
+      <c r="G268" t="s">
+        <v>534</v>
+      </c>
+      <c r="H268" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>300</v>
+      </c>
+      <c r="C269">
+        <v>126</v>
+      </c>
+      <c r="E269">
+        <v>12</v>
+      </c>
+      <c r="G269" t="s">
+        <v>534</v>
+      </c>
+      <c r="H269" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>300</v>
+      </c>
+      <c r="C270">
+        <v>127</v>
+      </c>
+      <c r="E270">
+        <v>24</v>
+      </c>
+      <c r="G270" t="s">
+        <v>534</v>
+      </c>
+      <c r="H270" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>300</v>
+      </c>
+      <c r="C271">
+        <v>128</v>
+      </c>
+      <c r="E271">
+        <v>4</v>
+      </c>
+      <c r="G271" t="s">
+        <v>534</v>
+      </c>
+      <c r="H271" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>363</v>
+      </c>
+      <c r="C272">
+        <v>212</v>
+      </c>
+      <c r="D272" t="s">
+        <v>211</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="G272" t="s">
+        <v>549</v>
+      </c>
+      <c r="H272" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>363</v>
+      </c>
+      <c r="C273">
+        <v>213</v>
+      </c>
+      <c r="D273" t="s">
+        <v>215</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="G273" t="s">
+        <v>549</v>
+      </c>
+      <c r="H273" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>363</v>
+      </c>
+      <c r="C274">
+        <v>214</v>
+      </c>
+      <c r="D274" t="s">
+        <v>169</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="G274" t="s">
+        <v>549</v>
+      </c>
+      <c r="H274" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>363</v>
+      </c>
+      <c r="C275">
+        <v>215</v>
+      </c>
+      <c r="D275" t="s">
+        <v>174</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="G275" t="s">
+        <v>549</v>
+      </c>
+      <c r="H275" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>363</v>
+      </c>
+      <c r="C276">
+        <v>216</v>
+      </c>
+      <c r="D276" t="s">
+        <v>183</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="G276" t="s">
+        <v>549</v>
+      </c>
+      <c r="H276" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>363</v>
+      </c>
+      <c r="C277">
+        <v>217</v>
+      </c>
+      <c r="D277" t="s">
+        <v>188</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="G277" t="s">
+        <v>549</v>
+      </c>
+      <c r="H277" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>363</v>
+      </c>
+      <c r="C278">
+        <v>218</v>
+      </c>
+      <c r="D278" t="s">
+        <v>192</v>
+      </c>
+      <c r="E278">
+        <v>1</v>
+      </c>
+      <c r="G278" t="s">
+        <v>549</v>
+      </c>
+      <c r="H278" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>363</v>
+      </c>
+      <c r="C279">
+        <v>220</v>
+      </c>
+      <c r="D279" t="s">
+        <v>196</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+      <c r="G279" t="s">
+        <v>549</v>
+      </c>
+      <c r="H279" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>363</v>
+      </c>
+      <c r="C280">
+        <v>222</v>
+      </c>
+      <c r="D280" t="s">
+        <v>200</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+      <c r="G280" t="s">
+        <v>549</v>
+      </c>
+      <c r="H280" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>307</v>
+      </c>
+      <c r="C281">
+        <v>200</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="G281" t="s">
+        <v>559</v>
+      </c>
+      <c r="H281" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>375</v>
+      </c>
+      <c r="C282">
+        <v>212</v>
+      </c>
+      <c r="D282" t="s">
+        <v>211</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+      <c r="F282">
+        <v>271</v>
+      </c>
+      <c r="G282" t="s">
+        <v>561</v>
+      </c>
+      <c r="H282" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>368</v>
+      </c>
+      <c r="C283">
+        <v>213</v>
+      </c>
+      <c r="D283" t="s">
+        <v>215</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+      <c r="F283">
+        <v>272</v>
+      </c>
+      <c r="G283" t="s">
+        <v>563</v>
+      </c>
+      <c r="H283" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>368</v>
+      </c>
+      <c r="C284">
+        <v>214</v>
+      </c>
+      <c r="D284" t="s">
+        <v>169</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284">
+        <v>273</v>
+      </c>
+      <c r="G284" t="s">
+        <v>563</v>
+      </c>
+      <c r="H284" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>368</v>
+      </c>
+      <c r="C285">
+        <v>215</v>
+      </c>
+      <c r="D285" t="s">
+        <v>174</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285">
+        <v>274</v>
+      </c>
+      <c r="G285" t="s">
+        <v>563</v>
+      </c>
+      <c r="H285" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>368</v>
+      </c>
+      <c r="C286">
+        <v>216</v>
+      </c>
+      <c r="D286" t="s">
+        <v>183</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+      <c r="F286">
+        <v>275</v>
+      </c>
+      <c r="G286" t="s">
+        <v>563</v>
+      </c>
+      <c r="H286" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>368</v>
+      </c>
+      <c r="C287">
+        <v>217</v>
+      </c>
+      <c r="D287" t="s">
+        <v>188</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+      <c r="F287">
+        <v>276</v>
+      </c>
+      <c r="G287" t="s">
+        <v>563</v>
+      </c>
+      <c r="H287" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>368</v>
+      </c>
+      <c r="C288">
+        <v>218</v>
+      </c>
+      <c r="D288" t="s">
+        <v>192</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+      <c r="F288">
+        <v>277</v>
+      </c>
+      <c r="G288" t="s">
+        <v>563</v>
+      </c>
+      <c r="H288" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>368</v>
+      </c>
+      <c r="C289">
+        <v>220</v>
+      </c>
+      <c r="D289" t="s">
+        <v>196</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+      <c r="F289">
+        <v>278</v>
+      </c>
+      <c r="G289" t="s">
+        <v>563</v>
+      </c>
+      <c r="H289" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>224</v>
+      </c>
+      <c r="C290">
+        <v>104</v>
+      </c>
+      <c r="E290">
+        <v>30</v>
+      </c>
+      <c r="G290" t="s">
+        <v>571</v>
+      </c>
+      <c r="H290" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>224</v>
+      </c>
+      <c r="C291">
+        <v>111</v>
+      </c>
+      <c r="E291">
+        <v>48</v>
+      </c>
+      <c r="G291" t="s">
+        <v>571</v>
+      </c>
+      <c r="H291" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>300</v>
+      </c>
+      <c r="C292">
+        <v>129</v>
+      </c>
+      <c r="E292">
+        <v>6</v>
+      </c>
+      <c r="G292" t="s">
+        <v>574</v>
+      </c>
+      <c r="H292" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>300</v>
+      </c>
+      <c r="C293">
+        <v>130</v>
+      </c>
+      <c r="E293">
+        <v>12</v>
+      </c>
+      <c r="G293" t="s">
+        <v>574</v>
+      </c>
+      <c r="H293" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>300</v>
+      </c>
+      <c r="C294">
+        <v>131</v>
+      </c>
+      <c r="E294">
+        <v>24</v>
+      </c>
+      <c r="G294" t="s">
+        <v>574</v>
+      </c>
+      <c r="H294" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>300</v>
+      </c>
+      <c r="C295">
+        <v>132</v>
+      </c>
+      <c r="E295">
+        <v>3</v>
+      </c>
+      <c r="G295" t="s">
+        <v>574</v>
+      </c>
+      <c r="H295" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>300</v>
+      </c>
+      <c r="C296">
+        <v>133</v>
+      </c>
+      <c r="E296">
+        <v>6</v>
+      </c>
+      <c r="G296" t="s">
+        <v>574</v>
+      </c>
+      <c r="H296" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>300</v>
+      </c>
+      <c r="C297">
+        <v>135</v>
+      </c>
+      <c r="E297">
+        <v>24</v>
+      </c>
+      <c r="G297" t="s">
+        <v>574</v>
+      </c>
+      <c r="H297" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>300</v>
+      </c>
+      <c r="C298">
+        <v>100</v>
+      </c>
+      <c r="E298">
+        <v>3</v>
+      </c>
+      <c r="G298" t="s">
+        <v>574</v>
+      </c>
+      <c r="H298" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>300</v>
+      </c>
+      <c r="C299">
+        <v>101</v>
+      </c>
+      <c r="E299">
+        <v>6</v>
+      </c>
+      <c r="G299" t="s">
+        <v>574</v>
+      </c>
+      <c r="H299" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>300</v>
+      </c>
+      <c r="C300">
+        <v>102</v>
+      </c>
+      <c r="E300">
+        <v>12</v>
+      </c>
+      <c r="G300" t="s">
+        <v>574</v>
+      </c>
+      <c r="H300" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>300</v>
+      </c>
+      <c r="C301">
+        <v>103</v>
+      </c>
+      <c r="E301">
+        <v>24</v>
+      </c>
+      <c r="G301" t="s">
+        <v>574</v>
+      </c>
+      <c r="H301" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>300</v>
+      </c>
+      <c r="C302">
+        <v>104</v>
+      </c>
+      <c r="E302">
+        <v>4</v>
+      </c>
+      <c r="G302" t="s">
+        <v>574</v>
+      </c>
+      <c r="H302" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>300</v>
+      </c>
+      <c r="C303">
+        <v>105</v>
+      </c>
+      <c r="E303">
+        <v>6</v>
+      </c>
+      <c r="G303" t="s">
+        <v>574</v>
+      </c>
+      <c r="H303" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
+        <v>300</v>
+      </c>
+      <c r="C304">
+        <v>106</v>
+      </c>
+      <c r="E304">
+        <v>12</v>
+      </c>
+      <c r="G304" t="s">
+        <v>574</v>
+      </c>
+      <c r="H304" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>300</v>
+      </c>
+      <c r="C305">
+        <v>107</v>
+      </c>
+      <c r="E305">
+        <v>24</v>
+      </c>
+      <c r="G305" t="s">
+        <v>574</v>
+      </c>
+      <c r="H305" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>363</v>
+      </c>
+      <c r="C306">
+        <v>224</v>
+      </c>
+      <c r="D306" t="s">
+        <v>215</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+      <c r="G306" t="s">
+        <v>589</v>
+      </c>
+      <c r="H306" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>363</v>
+      </c>
+      <c r="C307">
+        <v>225</v>
+      </c>
+      <c r="D307" t="s">
+        <v>169</v>
+      </c>
+      <c r="E307">
+        <v>1</v>
+      </c>
+      <c r="G307" t="s">
+        <v>589</v>
+      </c>
+      <c r="H307" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>363</v>
+      </c>
+      <c r="C308">
+        <v>226</v>
+      </c>
+      <c r="D308" t="s">
+        <v>174</v>
+      </c>
+      <c r="E308">
+        <v>1</v>
+      </c>
+      <c r="G308" t="s">
+        <v>589</v>
+      </c>
+      <c r="H308" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>363</v>
+      </c>
+      <c r="C309">
+        <v>227</v>
+      </c>
+      <c r="D309" t="s">
+        <v>183</v>
+      </c>
+      <c r="E309">
+        <v>1</v>
+      </c>
+      <c r="G309" t="s">
+        <v>589</v>
+      </c>
+      <c r="H309" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
+        <v>363</v>
+      </c>
+      <c r="C310">
+        <v>228</v>
+      </c>
+      <c r="D310" t="s">
+        <v>188</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="G310" t="s">
+        <v>589</v>
+      </c>
+      <c r="H310" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
+        <v>363</v>
+      </c>
+      <c r="C311">
+        <v>229</v>
+      </c>
+      <c r="D311" t="s">
+        <v>192</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+      <c r="G311" t="s">
+        <v>589</v>
+      </c>
+      <c r="H311" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>363</v>
+      </c>
+      <c r="C312">
+        <v>230</v>
+      </c>
+      <c r="D312" t="s">
+        <v>196</v>
+      </c>
+      <c r="E312">
+        <v>1</v>
+      </c>
+      <c r="G312" t="s">
+        <v>589</v>
+      </c>
+      <c r="H312" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>363</v>
+      </c>
+      <c r="C313">
+        <v>231</v>
+      </c>
+      <c r="D313" t="s">
+        <v>200</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+      <c r="G313" t="s">
+        <v>589</v>
+      </c>
+      <c r="H313" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
+        <v>363</v>
+      </c>
+      <c r="C314">
+        <v>232</v>
+      </c>
+      <c r="D314" t="s">
+        <v>204</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+      <c r="G314" t="s">
+        <v>589</v>
+      </c>
+      <c r="H314" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
+        <v>368</v>
+      </c>
+      <c r="C315">
+        <v>224</v>
+      </c>
+      <c r="D315" t="s">
+        <v>215</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+      <c r="F315">
+        <v>305</v>
+      </c>
+      <c r="G315" t="s">
+        <v>599</v>
+      </c>
+      <c r="H315" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
+        <v>368</v>
+      </c>
+      <c r="C316">
+        <v>225</v>
+      </c>
+      <c r="D316" t="s">
+        <v>169</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+      <c r="F316">
+        <v>306</v>
+      </c>
+      <c r="G316" t="s">
+        <v>599</v>
+      </c>
+      <c r="H316" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317" t="s">
+        <v>368</v>
+      </c>
+      <c r="C317">
+        <v>226</v>
+      </c>
+      <c r="D317" t="s">
+        <v>174</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+      <c r="F317">
+        <v>307</v>
+      </c>
+      <c r="G317" t="s">
+        <v>599</v>
+      </c>
+      <c r="H317" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318" t="s">
+        <v>368</v>
+      </c>
+      <c r="C318">
+        <v>227</v>
+      </c>
+      <c r="D318" t="s">
+        <v>183</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="F318">
+        <v>308</v>
+      </c>
+      <c r="G318" t="s">
+        <v>599</v>
+      </c>
+      <c r="H318" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319" t="s">
+        <v>368</v>
+      </c>
+      <c r="C319">
+        <v>228</v>
+      </c>
+      <c r="D319" t="s">
+        <v>188</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+      <c r="F319">
+        <v>309</v>
+      </c>
+      <c r="G319" t="s">
+        <v>599</v>
+      </c>
+      <c r="H319" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320" t="s">
+        <v>368</v>
+      </c>
+      <c r="C320">
+        <v>229</v>
+      </c>
+      <c r="D320" t="s">
+        <v>192</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+      <c r="F320">
+        <v>310</v>
+      </c>
+      <c r="G320" t="s">
+        <v>599</v>
+      </c>
+      <c r="H320" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" t="s">
+        <v>368</v>
+      </c>
+      <c r="C321">
+        <v>230</v>
+      </c>
+      <c r="D321" t="s">
+        <v>196</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+      <c r="F321">
+        <v>311</v>
+      </c>
+      <c r="G321" t="s">
+        <v>599</v>
+      </c>
+      <c r="H321" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322" t="s">
+        <v>368</v>
+      </c>
+      <c r="C322">
+        <v>231</v>
+      </c>
+      <c r="D322" t="s">
+        <v>200</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+      <c r="F322">
+        <v>312</v>
+      </c>
+      <c r="G322" t="s">
+        <v>599</v>
+      </c>
+      <c r="H322" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323" t="s">
+        <v>396</v>
+      </c>
+      <c r="C323">
+        <v>212</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+      <c r="G323" t="s">
+        <v>608</v>
+      </c>
+      <c r="H323" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
+        <v>224</v>
+      </c>
+      <c r="C324">
+        <v>106</v>
+      </c>
+      <c r="E324">
+        <v>24</v>
+      </c>
+      <c r="G324" t="s">
+        <v>610</v>
+      </c>
+      <c r="H324" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
+        <v>224</v>
+      </c>
+      <c r="C325">
+        <v>113</v>
+      </c>
+      <c r="E325">
+        <v>12</v>
+      </c>
+      <c r="G325" t="s">
+        <v>610</v>
+      </c>
+      <c r="H325" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
+        <v>300</v>
+      </c>
+      <c r="C326">
+        <v>108</v>
+      </c>
+      <c r="E326">
+        <v>3</v>
+      </c>
+      <c r="G326" t="s">
+        <v>613</v>
+      </c>
+      <c r="H326" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
+        <v>300</v>
+      </c>
+      <c r="C327">
+        <v>109</v>
+      </c>
+      <c r="E327">
+        <v>6</v>
+      </c>
+      <c r="G327" t="s">
+        <v>613</v>
+      </c>
+      <c r="H327" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
+        <v>300</v>
+      </c>
+      <c r="C328">
+        <v>110</v>
+      </c>
+      <c r="E328">
+        <v>12</v>
+      </c>
+      <c r="G328" t="s">
+        <v>613</v>
+      </c>
+      <c r="H328" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
+        <v>300</v>
+      </c>
+      <c r="C329">
+        <v>111</v>
+      </c>
+      <c r="E329">
+        <v>24</v>
+      </c>
+      <c r="G329" t="s">
+        <v>613</v>
+      </c>
+      <c r="H329" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
+        <v>300</v>
+      </c>
+      <c r="C330">
+        <v>112</v>
+      </c>
+      <c r="E330">
+        <v>4</v>
+      </c>
+      <c r="G330" t="s">
+        <v>613</v>
+      </c>
+      <c r="H330" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
+        <v>300</v>
+      </c>
+      <c r="C331">
+        <v>113</v>
+      </c>
+      <c r="E331">
+        <v>6</v>
+      </c>
+      <c r="G331" t="s">
+        <v>613</v>
+      </c>
+      <c r="H331" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
+        <v>300</v>
+      </c>
+      <c r="C332">
+        <v>114</v>
+      </c>
+      <c r="E332">
+        <v>12</v>
+      </c>
+      <c r="G332" t="s">
+        <v>613</v>
+      </c>
+      <c r="H332" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>300</v>
+      </c>
+      <c r="C333">
+        <v>115</v>
+      </c>
+      <c r="E333">
+        <v>24</v>
+      </c>
+      <c r="G333" t="s">
+        <v>613</v>
+      </c>
+      <c r="H333" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
+        <v>300</v>
+      </c>
+      <c r="C334">
+        <v>116</v>
+      </c>
+      <c r="E334">
+        <v>5</v>
+      </c>
+      <c r="G334" t="s">
+        <v>613</v>
+      </c>
+      <c r="H334" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
+        <v>300</v>
+      </c>
+      <c r="C335">
+        <v>118</v>
+      </c>
+      <c r="E335">
+        <v>12</v>
+      </c>
+      <c r="G335" t="s">
+        <v>613</v>
+      </c>
+      <c r="H335" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336" t="s">
+        <v>300</v>
+      </c>
+      <c r="C336">
+        <v>119</v>
+      </c>
+      <c r="E336">
+        <v>24</v>
+      </c>
+      <c r="G336" t="s">
+        <v>613</v>
+      </c>
+      <c r="H336" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337" t="s">
+        <v>300</v>
+      </c>
+      <c r="C337">
+        <v>120</v>
+      </c>
+      <c r="E337">
+        <v>5</v>
+      </c>
+      <c r="G337" t="s">
+        <v>613</v>
+      </c>
+      <c r="H337" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338" t="s">
+        <v>300</v>
+      </c>
+      <c r="C338">
+        <v>121</v>
+      </c>
+      <c r="E338">
+        <v>6</v>
+      </c>
+      <c r="G338" t="s">
+        <v>613</v>
+      </c>
+      <c r="H338" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339" t="s">
+        <v>300</v>
+      </c>
+      <c r="C339">
+        <v>122</v>
+      </c>
+      <c r="E339">
+        <v>12</v>
+      </c>
+      <c r="G339" t="s">
+        <v>613</v>
+      </c>
+      <c r="H339" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s">
+        <v>363</v>
+      </c>
+      <c r="C340">
+        <v>233</v>
+      </c>
+      <c r="D340" t="s">
+        <v>169</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+      <c r="G340" t="s">
+        <v>628</v>
+      </c>
+      <c r="H340" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
+        <v>363</v>
+      </c>
+      <c r="C341">
+        <v>234</v>
+      </c>
+      <c r="D341" t="s">
+        <v>174</v>
+      </c>
+      <c r="E341">
+        <v>1</v>
+      </c>
+      <c r="G341" t="s">
+        <v>628</v>
+      </c>
+      <c r="H341" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342" t="s">
+        <v>363</v>
+      </c>
+      <c r="C342">
+        <v>235</v>
+      </c>
+      <c r="D342" t="s">
+        <v>183</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+      <c r="G342" t="s">
+        <v>628</v>
+      </c>
+      <c r="H342" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343" t="s">
+        <v>363</v>
+      </c>
+      <c r="C343">
+        <v>200</v>
+      </c>
+      <c r="D343" t="s">
+        <v>188</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+      <c r="G343" t="s">
+        <v>628</v>
+      </c>
+      <c r="H343" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" t="s">
+        <v>363</v>
+      </c>
+      <c r="C344">
+        <v>201</v>
+      </c>
+      <c r="D344" t="s">
+        <v>192</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+      <c r="G344" t="s">
+        <v>628</v>
+      </c>
+      <c r="H344" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
+        <v>363</v>
+      </c>
+      <c r="C345">
+        <v>202</v>
+      </c>
+      <c r="D345" t="s">
+        <v>196</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+      <c r="G345" t="s">
+        <v>628</v>
+      </c>
+      <c r="H345" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C346">
+        <v>203</v>
+      </c>
+      <c r="D346" t="s">
+        <v>200</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="G346" t="s">
+        <v>628</v>
+      </c>
+      <c r="H346" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347" t="s">
+        <v>363</v>
+      </c>
+      <c r="C347">
+        <v>204</v>
+      </c>
+      <c r="D347" t="s">
+        <v>204</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="G347" t="s">
+        <v>628</v>
+      </c>
+      <c r="H347" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348" t="s">
+        <v>363</v>
+      </c>
+      <c r="C348">
+        <v>205</v>
+      </c>
+      <c r="D348" t="s">
+        <v>211</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+      <c r="G348" t="s">
+        <v>628</v>
+      </c>
+      <c r="H348" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349" t="s">
+        <v>307</v>
+      </c>
+      <c r="C349">
+        <v>205</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+      <c r="G349" t="s">
+        <v>559</v>
+      </c>
+      <c r="H349" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350" t="s">
+        <v>368</v>
+      </c>
+      <c r="C350">
+        <v>233</v>
+      </c>
+      <c r="D350" t="s">
+        <v>169</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350">
+        <v>339</v>
+      </c>
+      <c r="G350" t="s">
+        <v>639</v>
+      </c>
+      <c r="H350" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351" t="s">
+        <v>368</v>
+      </c>
+      <c r="C351">
+        <v>234</v>
+      </c>
+      <c r="D351" t="s">
+        <v>174</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+      <c r="F351">
+        <v>340</v>
+      </c>
+      <c r="G351" t="s">
+        <v>639</v>
+      </c>
+      <c r="H351" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352" t="s">
+        <v>368</v>
+      </c>
+      <c r="C352">
+        <v>235</v>
+      </c>
+      <c r="D352" t="s">
+        <v>183</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+      <c r="F352">
+        <v>341</v>
+      </c>
+      <c r="G352" t="s">
+        <v>639</v>
+      </c>
+      <c r="H352" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C353">
+        <v>200</v>
+      </c>
+      <c r="D353" t="s">
+        <v>188</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+      <c r="F353">
+        <v>342</v>
+      </c>
+      <c r="G353" t="s">
+        <v>639</v>
+      </c>
+      <c r="H353" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354" t="s">
+        <v>368</v>
+      </c>
+      <c r="C354">
+        <v>201</v>
+      </c>
+      <c r="D354" t="s">
+        <v>192</v>
+      </c>
+      <c r="E354">
+        <v>1</v>
+      </c>
+      <c r="F354">
+        <v>343</v>
+      </c>
+      <c r="G354" t="s">
+        <v>639</v>
+      </c>
+      <c r="H354" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355" t="s">
+        <v>368</v>
+      </c>
+      <c r="C355">
+        <v>202</v>
+      </c>
+      <c r="D355" t="s">
+        <v>196</v>
+      </c>
+      <c r="E355">
+        <v>1</v>
+      </c>
+      <c r="F355">
+        <v>344</v>
+      </c>
+      <c r="G355" t="s">
+        <v>639</v>
+      </c>
+      <c r="H355" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356" t="s">
+        <v>368</v>
+      </c>
+      <c r="C356">
+        <v>203</v>
+      </c>
+      <c r="D356" t="s">
+        <v>200</v>
+      </c>
+      <c r="E356">
+        <v>1</v>
+      </c>
+      <c r="F356">
+        <v>345</v>
+      </c>
+      <c r="G356" t="s">
+        <v>639</v>
+      </c>
+      <c r="H356" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357" t="s">
+        <v>368</v>
+      </c>
+      <c r="C357">
+        <v>204</v>
+      </c>
+      <c r="D357" t="s">
+        <v>204</v>
+      </c>
+      <c r="E357">
+        <v>1</v>
+      </c>
+      <c r="F357">
+        <v>346</v>
+      </c>
+      <c r="G357" t="s">
+        <v>639</v>
+      </c>
+      <c r="H357" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358" t="s">
+        <v>224</v>
+      </c>
+      <c r="C358">
+        <v>108</v>
+      </c>
+      <c r="E358">
+        <v>30</v>
+      </c>
+      <c r="G358" t="s">
+        <v>648</v>
+      </c>
+      <c r="H358" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359" t="s">
+        <v>224</v>
+      </c>
+      <c r="C359">
+        <v>115</v>
+      </c>
+      <c r="E359">
+        <v>48</v>
+      </c>
+      <c r="G359" t="s">
+        <v>648</v>
+      </c>
+      <c r="H359" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
+        <v>300</v>
+      </c>
+      <c r="C360">
+        <v>123</v>
+      </c>
+      <c r="E360">
+        <v>24</v>
+      </c>
+      <c r="G360" t="s">
+        <v>651</v>
+      </c>
+      <c r="H360" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
+        <v>300</v>
+      </c>
+      <c r="C361">
+        <v>124</v>
+      </c>
+      <c r="E361">
+        <v>4</v>
+      </c>
+      <c r="G361" t="s">
+        <v>651</v>
+      </c>
+      <c r="H361" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
+        <v>300</v>
+      </c>
+      <c r="C362">
+        <v>125</v>
+      </c>
+      <c r="E362">
+        <v>6</v>
+      </c>
+      <c r="G362" t="s">
+        <v>651</v>
+      </c>
+      <c r="H362" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
+        <v>300</v>
+      </c>
+      <c r="C363">
+        <v>126</v>
+      </c>
+      <c r="E363">
+        <v>12</v>
+      </c>
+      <c r="G363" t="s">
+        <v>651</v>
+      </c>
+      <c r="H363" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
+        <v>300</v>
+      </c>
+      <c r="C364">
+        <v>127</v>
+      </c>
+      <c r="E364">
+        <v>24</v>
+      </c>
+      <c r="G364" t="s">
+        <v>651</v>
+      </c>
+      <c r="H364" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
+        <v>300</v>
+      </c>
+      <c r="C365">
+        <v>128</v>
+      </c>
+      <c r="E365">
+        <v>5</v>
+      </c>
+      <c r="G365" t="s">
+        <v>651</v>
+      </c>
+      <c r="H365" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
+        <v>300</v>
+      </c>
+      <c r="C366">
+        <v>129</v>
+      </c>
+      <c r="E366">
+        <v>6</v>
+      </c>
+      <c r="G366" t="s">
+        <v>651</v>
+      </c>
+      <c r="H366" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>300</v>
+      </c>
+      <c r="C367">
+        <v>130</v>
+      </c>
+      <c r="E367">
+        <v>12</v>
+      </c>
+      <c r="G367" t="s">
+        <v>651</v>
+      </c>
+      <c r="H367" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>300</v>
+      </c>
+      <c r="C368">
+        <v>131</v>
+      </c>
+      <c r="E368">
+        <v>24</v>
+      </c>
+      <c r="G368" t="s">
+        <v>651</v>
+      </c>
+      <c r="H368" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>300</v>
+      </c>
+      <c r="C369">
+        <v>132</v>
+      </c>
+      <c r="E369">
+        <v>3</v>
+      </c>
+      <c r="G369" t="s">
+        <v>651</v>
+      </c>
+      <c r="H369" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>300</v>
+      </c>
+      <c r="C370">
+        <v>133</v>
+      </c>
+      <c r="E370">
+        <v>6</v>
+      </c>
+      <c r="G370" t="s">
+        <v>651</v>
+      </c>
+      <c r="H370" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
+        <v>300</v>
+      </c>
+      <c r="C371">
+        <v>135</v>
+      </c>
+      <c r="E371">
+        <v>24</v>
+      </c>
+      <c r="G371" t="s">
+        <v>651</v>
+      </c>
+      <c r="H371" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
+        <v>300</v>
+      </c>
+      <c r="C372">
+        <v>100</v>
+      </c>
+      <c r="E372">
+        <v>3</v>
+      </c>
+      <c r="G372" t="s">
+        <v>651</v>
+      </c>
+      <c r="H372" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373" t="s">
+        <v>300</v>
+      </c>
+      <c r="C373">
+        <v>101</v>
+      </c>
+      <c r="E373">
+        <v>6</v>
+      </c>
+      <c r="G373" t="s">
+        <v>651</v>
+      </c>
+      <c r="H373" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374" t="s">
+        <v>363</v>
+      </c>
+      <c r="C374">
+        <v>206</v>
+      </c>
+      <c r="D374" t="s">
+        <v>174</v>
+      </c>
+      <c r="E374">
+        <v>1</v>
+      </c>
+      <c r="G374" t="s">
+        <v>666</v>
+      </c>
+      <c r="H374" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375" t="s">
+        <v>363</v>
+      </c>
+      <c r="C375">
+        <v>208</v>
+      </c>
+      <c r="D375" t="s">
+        <v>183</v>
+      </c>
+      <c r="E375">
+        <v>1</v>
+      </c>
+      <c r="G375" t="s">
+        <v>666</v>
+      </c>
+      <c r="H375" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376" t="s">
+        <v>363</v>
+      </c>
+      <c r="C376">
+        <v>210</v>
+      </c>
+      <c r="D376" t="s">
+        <v>188</v>
+      </c>
+      <c r="E376">
+        <v>1</v>
+      </c>
+      <c r="G376" t="s">
+        <v>666</v>
+      </c>
+      <c r="H376" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377" t="s">
+        <v>363</v>
+      </c>
+      <c r="C377">
+        <v>212</v>
+      </c>
+      <c r="D377" t="s">
+        <v>192</v>
+      </c>
+      <c r="E377">
+        <v>1</v>
+      </c>
+      <c r="G377" t="s">
+        <v>666</v>
+      </c>
+      <c r="H377" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378" t="s">
+        <v>363</v>
+      </c>
+      <c r="C378">
+        <v>213</v>
+      </c>
+      <c r="D378" t="s">
+        <v>196</v>
+      </c>
+      <c r="E378">
+        <v>1</v>
+      </c>
+      <c r="G378" t="s">
+        <v>666</v>
+      </c>
+      <c r="H378" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" t="s">
+        <v>363</v>
+      </c>
+      <c r="C379">
+        <v>214</v>
+      </c>
+      <c r="D379" t="s">
+        <v>200</v>
+      </c>
+      <c r="E379">
+        <v>1</v>
+      </c>
+      <c r="G379" t="s">
+        <v>666</v>
+      </c>
+      <c r="H379" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380" t="s">
+        <v>363</v>
+      </c>
+      <c r="C380">
+        <v>215</v>
+      </c>
+      <c r="D380" t="s">
+        <v>204</v>
+      </c>
+      <c r="E380">
+        <v>1</v>
+      </c>
+      <c r="G380" t="s">
+        <v>666</v>
+      </c>
+      <c r="H380" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381" t="s">
+        <v>363</v>
+      </c>
+      <c r="C381">
+        <v>216</v>
+      </c>
+      <c r="D381" t="s">
+        <v>211</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+      <c r="G381" t="s">
+        <v>666</v>
+      </c>
+      <c r="H381" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382" t="s">
+        <v>363</v>
+      </c>
+      <c r="C382">
+        <v>217</v>
+      </c>
+      <c r="D382" t="s">
+        <v>215</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+      <c r="G382" t="s">
+        <v>666</v>
+      </c>
+      <c r="H382" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383" t="s">
+        <v>375</v>
+      </c>
+      <c r="C383">
+        <v>206</v>
+      </c>
+      <c r="D383" t="s">
+        <v>174</v>
+      </c>
+      <c r="E383">
+        <v>1</v>
+      </c>
+      <c r="F383">
+        <v>373</v>
+      </c>
+      <c r="G383" t="s">
+        <v>676</v>
+      </c>
+      <c r="H383" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" t="s">
+        <v>368</v>
+      </c>
+      <c r="C384">
+        <v>208</v>
+      </c>
+      <c r="D384" t="s">
+        <v>183</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+      <c r="F384">
+        <v>374</v>
+      </c>
+      <c r="G384" t="s">
+        <v>678</v>
+      </c>
+      <c r="H384" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385" t="s">
+        <v>368</v>
+      </c>
+      <c r="C385">
+        <v>210</v>
+      </c>
+      <c r="D385" t="s">
+        <v>188</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+      <c r="F385">
+        <v>375</v>
+      </c>
+      <c r="G385" t="s">
+        <v>678</v>
+      </c>
+      <c r="H385" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386" t="s">
+        <v>368</v>
+      </c>
+      <c r="C386">
+        <v>212</v>
+      </c>
+      <c r="D386" t="s">
+        <v>192</v>
+      </c>
+      <c r="E386">
+        <v>1</v>
+      </c>
+      <c r="F386">
+        <v>376</v>
+      </c>
+      <c r="G386" t="s">
+        <v>678</v>
+      </c>
+      <c r="H386" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387" t="s">
+        <v>368</v>
+      </c>
+      <c r="C387">
+        <v>213</v>
+      </c>
+      <c r="D387" t="s">
+        <v>196</v>
+      </c>
+      <c r="E387">
+        <v>1</v>
+      </c>
+      <c r="F387">
+        <v>377</v>
+      </c>
+      <c r="G387" t="s">
+        <v>678</v>
+      </c>
+      <c r="H387" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388" t="s">
+        <v>368</v>
+      </c>
+      <c r="C388">
+        <v>214</v>
+      </c>
+      <c r="D388" t="s">
+        <v>200</v>
+      </c>
+      <c r="E388">
+        <v>1</v>
+      </c>
+      <c r="F388">
+        <v>378</v>
+      </c>
+      <c r="G388" t="s">
+        <v>678</v>
+      </c>
+      <c r="H388" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389" t="s">
+        <v>368</v>
+      </c>
+      <c r="C389">
+        <v>215</v>
+      </c>
+      <c r="D389" t="s">
+        <v>204</v>
+      </c>
+      <c r="E389">
+        <v>1</v>
+      </c>
+      <c r="F389">
+        <v>379</v>
+      </c>
+      <c r="G389" t="s">
+        <v>678</v>
+      </c>
+      <c r="H389" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" t="s">
+        <v>368</v>
+      </c>
+      <c r="C390">
+        <v>216</v>
+      </c>
+      <c r="D390" t="s">
+        <v>211</v>
+      </c>
+      <c r="E390">
+        <v>1</v>
+      </c>
+      <c r="F390">
+        <v>380</v>
+      </c>
+      <c r="G390" t="s">
+        <v>678</v>
+      </c>
+      <c r="H390" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391" t="s">
+        <v>224</v>
+      </c>
+      <c r="C391">
+        <v>110</v>
+      </c>
+      <c r="E391">
+        <v>24</v>
+      </c>
+      <c r="G391" t="s">
+        <v>686</v>
+      </c>
+      <c r="H391" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392" t="s">
+        <v>224</v>
+      </c>
+      <c r="C392">
+        <v>118</v>
+      </c>
+      <c r="E392">
+        <v>24</v>
+      </c>
+      <c r="G392" t="s">
+        <v>686</v>
+      </c>
+      <c r="H392" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393" t="s">
+        <v>300</v>
+      </c>
+      <c r="C393">
+        <v>102</v>
+      </c>
+      <c r="E393">
+        <v>12</v>
+      </c>
+      <c r="G393" t="s">
+        <v>689</v>
+      </c>
+      <c r="H393" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394" t="s">
+        <v>300</v>
+      </c>
+      <c r="C394">
+        <v>103</v>
+      </c>
+      <c r="E394">
+        <v>24</v>
+      </c>
+      <c r="G394" t="s">
+        <v>689</v>
+      </c>
+      <c r="H394" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395" t="s">
+        <v>300</v>
+      </c>
+      <c r="C395">
+        <v>104</v>
+      </c>
+      <c r="E395">
+        <v>5</v>
+      </c>
+      <c r="G395" t="s">
+        <v>689</v>
+      </c>
+      <c r="H395" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396" t="s">
+        <v>300</v>
+      </c>
+      <c r="C396">
+        <v>105</v>
+      </c>
+      <c r="E396">
+        <v>6</v>
+      </c>
+      <c r="G396" t="s">
+        <v>689</v>
+      </c>
+      <c r="H396" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397" t="s">
+        <v>300</v>
+      </c>
+      <c r="C397">
+        <v>106</v>
+      </c>
+      <c r="E397">
+        <v>12</v>
+      </c>
+      <c r="G397" t="s">
+        <v>689</v>
+      </c>
+      <c r="H397" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398" t="s">
+        <v>300</v>
+      </c>
+      <c r="C398">
+        <v>107</v>
+      </c>
+      <c r="E398">
+        <v>24</v>
+      </c>
+      <c r="G398" t="s">
+        <v>689</v>
+      </c>
+      <c r="H398" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399" t="s">
+        <v>300</v>
+      </c>
+      <c r="C399">
+        <v>108</v>
+      </c>
+      <c r="E399">
+        <v>3</v>
+      </c>
+      <c r="G399" t="s">
+        <v>689</v>
+      </c>
+      <c r="H399" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400" t="s">
+        <v>300</v>
+      </c>
+      <c r="C400">
+        <v>109</v>
+      </c>
+      <c r="E400">
+        <v>6</v>
+      </c>
+      <c r="G400" t="s">
+        <v>689</v>
+      </c>
+      <c r="H400" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401" t="s">
+        <v>300</v>
+      </c>
+      <c r="C401">
+        <v>110</v>
+      </c>
+      <c r="E401">
+        <v>12</v>
+      </c>
+      <c r="G401" t="s">
+        <v>689</v>
+      </c>
+      <c r="H401" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" t="s">
+        <v>300</v>
+      </c>
+      <c r="C402">
+        <v>111</v>
+      </c>
+      <c r="E402">
+        <v>24</v>
+      </c>
+      <c r="G402" t="s">
+        <v>689</v>
+      </c>
+      <c r="H402" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" t="s">
+        <v>300</v>
+      </c>
+      <c r="C403">
+        <v>112</v>
+      </c>
+      <c r="E403">
+        <v>4</v>
+      </c>
+      <c r="G403" t="s">
+        <v>689</v>
+      </c>
+      <c r="H403" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" t="s">
+        <v>300</v>
+      </c>
+      <c r="C404">
+        <v>113</v>
+      </c>
+      <c r="E404">
+        <v>6</v>
+      </c>
+      <c r="G404" t="s">
+        <v>689</v>
+      </c>
+      <c r="H404" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" t="s">
+        <v>300</v>
+      </c>
+      <c r="C405">
+        <v>114</v>
+      </c>
+      <c r="E405">
+        <v>12</v>
+      </c>
+      <c r="G405" t="s">
+        <v>689</v>
+      </c>
+      <c r="H405" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" t="s">
+        <v>300</v>
+      </c>
+      <c r="C406">
+        <v>115</v>
+      </c>
+      <c r="E406">
+        <v>24</v>
+      </c>
+      <c r="G406" t="s">
+        <v>689</v>
+      </c>
+      <c r="H406" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" t="s">
+        <v>363</v>
+      </c>
+      <c r="C407">
+        <v>218</v>
+      </c>
+      <c r="D407" t="s">
+        <v>183</v>
+      </c>
+      <c r="E407">
+        <v>1</v>
+      </c>
+      <c r="G407" t="s">
+        <v>704</v>
+      </c>
+      <c r="H407" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" t="s">
+        <v>363</v>
+      </c>
+      <c r="C408">
+        <v>220</v>
+      </c>
+      <c r="D408" t="s">
+        <v>188</v>
+      </c>
+      <c r="E408">
+        <v>1</v>
+      </c>
+      <c r="G408" t="s">
+        <v>704</v>
+      </c>
+      <c r="H408" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" t="s">
+        <v>363</v>
+      </c>
+      <c r="C409">
+        <v>222</v>
+      </c>
+      <c r="D409" t="s">
+        <v>192</v>
+      </c>
+      <c r="E409">
+        <v>1</v>
+      </c>
+      <c r="G409" t="s">
+        <v>704</v>
+      </c>
+      <c r="H409" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410" t="s">
+        <v>363</v>
+      </c>
+      <c r="C410">
+        <v>224</v>
+      </c>
+      <c r="D410" t="s">
+        <v>196</v>
+      </c>
+      <c r="E410">
+        <v>1</v>
+      </c>
+      <c r="G410" t="s">
+        <v>704</v>
+      </c>
+      <c r="H410" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411" t="s">
+        <v>363</v>
+      </c>
+      <c r="C411">
+        <v>225</v>
+      </c>
+      <c r="D411" t="s">
+        <v>200</v>
+      </c>
+      <c r="E411">
+        <v>1</v>
+      </c>
+      <c r="G411" t="s">
+        <v>704</v>
+      </c>
+      <c r="H411" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412" t="s">
+        <v>363</v>
+      </c>
+      <c r="C412">
+        <v>226</v>
+      </c>
+      <c r="D412" t="s">
+        <v>204</v>
+      </c>
+      <c r="E412">
+        <v>1</v>
+      </c>
+      <c r="G412" t="s">
+        <v>704</v>
+      </c>
+      <c r="H412" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413" t="s">
+        <v>363</v>
+      </c>
+      <c r="C413">
+        <v>227</v>
+      </c>
+      <c r="D413" t="s">
+        <v>211</v>
+      </c>
+      <c r="E413">
+        <v>1</v>
+      </c>
+      <c r="G413" t="s">
+        <v>704</v>
+      </c>
+      <c r="H413" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414" t="s">
+        <v>363</v>
+      </c>
+      <c r="C414">
+        <v>228</v>
+      </c>
+      <c r="D414" t="s">
+        <v>215</v>
+      </c>
+      <c r="E414">
+        <v>1</v>
+      </c>
+      <c r="G414" t="s">
+        <v>704</v>
+      </c>
+      <c r="H414" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415" t="s">
+        <v>363</v>
+      </c>
+      <c r="C415">
+        <v>229</v>
+      </c>
+      <c r="D415" t="s">
+        <v>169</v>
+      </c>
+      <c r="E415">
+        <v>1</v>
+      </c>
+      <c r="G415" t="s">
+        <v>704</v>
+      </c>
+      <c r="H415" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416" t="s">
+        <v>307</v>
+      </c>
+      <c r="C416">
+        <v>213</v>
+      </c>
+      <c r="E416">
+        <v>1</v>
+      </c>
+      <c r="G416" t="s">
+        <v>559</v>
+      </c>
+      <c r="H416" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" t="s">
+        <v>368</v>
+      </c>
+      <c r="C417">
+        <v>218</v>
+      </c>
+      <c r="D417" t="s">
+        <v>183</v>
+      </c>
+      <c r="E417">
+        <v>1</v>
+      </c>
+      <c r="F417">
+        <v>406</v>
+      </c>
+      <c r="G417" t="s">
+        <v>715</v>
+      </c>
+      <c r="H417" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" t="s">
+        <v>368</v>
+      </c>
+      <c r="C418">
+        <v>220</v>
+      </c>
+      <c r="D418" t="s">
+        <v>188</v>
+      </c>
+      <c r="E418">
+        <v>1</v>
+      </c>
+      <c r="F418">
+        <v>407</v>
+      </c>
+      <c r="G418" t="s">
+        <v>715</v>
+      </c>
+      <c r="H418" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" t="s">
+        <v>368</v>
+      </c>
+      <c r="C419">
+        <v>222</v>
+      </c>
+      <c r="D419" t="s">
+        <v>192</v>
+      </c>
+      <c r="E419">
+        <v>1</v>
+      </c>
+      <c r="F419">
+        <v>408</v>
+      </c>
+      <c r="G419" t="s">
+        <v>715</v>
+      </c>
+      <c r="H419" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" t="s">
+        <v>368</v>
+      </c>
+      <c r="C420">
+        <v>224</v>
+      </c>
+      <c r="D420" t="s">
+        <v>196</v>
+      </c>
+      <c r="E420">
+        <v>1</v>
+      </c>
+      <c r="F420">
+        <v>409</v>
+      </c>
+      <c r="G420" t="s">
+        <v>715</v>
+      </c>
+      <c r="H420" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>368</v>
+      </c>
+      <c r="C421">
+        <v>225</v>
+      </c>
+      <c r="D421" t="s">
+        <v>200</v>
+      </c>
+      <c r="E421">
+        <v>1</v>
+      </c>
+      <c r="F421">
+        <v>410</v>
+      </c>
+      <c r="G421" t="s">
+        <v>715</v>
+      </c>
+      <c r="H421" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" t="s">
+        <v>368</v>
+      </c>
+      <c r="C422">
+        <v>226</v>
+      </c>
+      <c r="D422" t="s">
+        <v>204</v>
+      </c>
+      <c r="E422">
+        <v>1</v>
+      </c>
+      <c r="F422">
+        <v>411</v>
+      </c>
+      <c r="G422" t="s">
+        <v>715</v>
+      </c>
+      <c r="H422" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" t="s">
+        <v>368</v>
+      </c>
+      <c r="C423">
+        <v>227</v>
+      </c>
+      <c r="D423" t="s">
+        <v>211</v>
+      </c>
+      <c r="E423">
+        <v>1</v>
+      </c>
+      <c r="F423">
+        <v>412</v>
+      </c>
+      <c r="G423" t="s">
+        <v>715</v>
+      </c>
+      <c r="H423" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" t="s">
+        <v>368</v>
+      </c>
+      <c r="C424">
+        <v>228</v>
+      </c>
+      <c r="D424" t="s">
+        <v>215</v>
+      </c>
+      <c r="E424">
+        <v>1</v>
+      </c>
+      <c r="F424">
+        <v>413</v>
+      </c>
+      <c r="G424" t="s">
+        <v>715</v>
+      </c>
+      <c r="H424" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" t="s">
+        <v>396</v>
+      </c>
+      <c r="C425">
+        <v>206</v>
+      </c>
+      <c r="E425">
+        <v>1</v>
+      </c>
+      <c r="G425" t="s">
+        <v>608</v>
+      </c>
+      <c r="H425" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" t="s">
+        <v>224</v>
+      </c>
+      <c r="C426">
+        <v>112</v>
+      </c>
+      <c r="E426">
+        <v>30</v>
+      </c>
+      <c r="G426" t="s">
+        <v>725</v>
+      </c>
+      <c r="H426" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" t="s">
+        <v>224</v>
+      </c>
+      <c r="C427">
+        <v>120</v>
+      </c>
+      <c r="E427">
+        <v>30</v>
+      </c>
+      <c r="G427" t="s">
+        <v>725</v>
+      </c>
+      <c r="H427" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" t="s">
+        <v>300</v>
+      </c>
+      <c r="C428">
+        <v>116</v>
+      </c>
+      <c r="E428">
+        <v>3</v>
+      </c>
+      <c r="G428" t="s">
+        <v>728</v>
+      </c>
+      <c r="H428" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>300</v>
+      </c>
+      <c r="C429">
+        <v>118</v>
+      </c>
+      <c r="E429">
+        <v>12</v>
+      </c>
+      <c r="G429" t="s">
+        <v>728</v>
+      </c>
+      <c r="H429" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>300</v>
+      </c>
+      <c r="C430">
+        <v>119</v>
+      </c>
+      <c r="E430">
+        <v>24</v>
+      </c>
+      <c r="G430" t="s">
+        <v>728</v>
+      </c>
+      <c r="H430" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" t="s">
+        <v>300</v>
+      </c>
+      <c r="C431">
+        <v>120</v>
+      </c>
+      <c r="E431">
+        <v>3</v>
+      </c>
+      <c r="G431" t="s">
+        <v>728</v>
+      </c>
+      <c r="H431" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" t="s">
+        <v>300</v>
+      </c>
+      <c r="C432">
+        <v>121</v>
+      </c>
+      <c r="E432">
+        <v>6</v>
+      </c>
+      <c r="G432" t="s">
+        <v>728</v>
+      </c>
+      <c r="H432" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>300</v>
+      </c>
+      <c r="C433">
+        <v>122</v>
+      </c>
+      <c r="E433">
+        <v>12</v>
+      </c>
+      <c r="G433" t="s">
+        <v>728</v>
+      </c>
+      <c r="H433" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" t="s">
+        <v>300</v>
+      </c>
+      <c r="C434">
+        <v>123</v>
+      </c>
+      <c r="E434">
+        <v>24</v>
+      </c>
+      <c r="G434" t="s">
+        <v>728</v>
+      </c>
+      <c r="H434" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" t="s">
+        <v>300</v>
+      </c>
+      <c r="C435">
+        <v>124</v>
+      </c>
+      <c r="E435">
+        <v>4</v>
+      </c>
+      <c r="G435" t="s">
+        <v>728</v>
+      </c>
+      <c r="H435" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" t="s">
+        <v>300</v>
+      </c>
+      <c r="C436">
+        <v>125</v>
+      </c>
+      <c r="E436">
+        <v>6</v>
+      </c>
+      <c r="G436" t="s">
+        <v>728</v>
+      </c>
+      <c r="H436" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" t="s">
+        <v>300</v>
+      </c>
+      <c r="C437">
+        <v>126</v>
+      </c>
+      <c r="E437">
+        <v>12</v>
+      </c>
+      <c r="G437" t="s">
+        <v>728</v>
+      </c>
+      <c r="H437" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" t="s">
+        <v>300</v>
+      </c>
+      <c r="C438">
+        <v>127</v>
+      </c>
+      <c r="E438">
+        <v>24</v>
+      </c>
+      <c r="G438" t="s">
+        <v>728</v>
+      </c>
+      <c r="H438" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439" t="s">
+        <v>300</v>
+      </c>
+      <c r="C439">
+        <v>128</v>
+      </c>
+      <c r="E439">
+        <v>5</v>
+      </c>
+      <c r="G439" t="s">
+        <v>728</v>
+      </c>
+      <c r="H439" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440" t="s">
+        <v>300</v>
+      </c>
+      <c r="C440">
+        <v>129</v>
+      </c>
+      <c r="E440">
+        <v>6</v>
+      </c>
+      <c r="G440" t="s">
+        <v>728</v>
+      </c>
+      <c r="H440" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441" t="s">
+        <v>300</v>
+      </c>
+      <c r="C441">
+        <v>130</v>
+      </c>
+      <c r="E441">
+        <v>12</v>
+      </c>
+      <c r="G441" t="s">
+        <v>728</v>
+      </c>
+      <c r="H441" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442" t="s">
+        <v>363</v>
+      </c>
+      <c r="C442">
+        <v>230</v>
+      </c>
+      <c r="D442" t="s">
+        <v>188</v>
+      </c>
+      <c r="E442">
+        <v>1</v>
+      </c>
+      <c r="G442" t="s">
+        <v>743</v>
+      </c>
+      <c r="H442" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443" t="s">
+        <v>363</v>
+      </c>
+      <c r="C443">
+        <v>231</v>
+      </c>
+      <c r="D443" t="s">
+        <v>192</v>
+      </c>
+      <c r="E443">
+        <v>1</v>
+      </c>
+      <c r="G443" t="s">
+        <v>743</v>
+      </c>
+      <c r="H443" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444" t="s">
+        <v>363</v>
+      </c>
+      <c r="C444">
+        <v>232</v>
+      </c>
+      <c r="D444" t="s">
+        <v>196</v>
+      </c>
+      <c r="E444">
+        <v>1</v>
+      </c>
+      <c r="G444" t="s">
+        <v>743</v>
+      </c>
+      <c r="H444" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" t="s">
+        <v>363</v>
+      </c>
+      <c r="C445">
+        <v>233</v>
+      </c>
+      <c r="D445" t="s">
+        <v>200</v>
+      </c>
+      <c r="E445">
+        <v>1</v>
+      </c>
+      <c r="G445" t="s">
+        <v>743</v>
+      </c>
+      <c r="H445" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446" t="s">
+        <v>363</v>
+      </c>
+      <c r="C446">
+        <v>234</v>
+      </c>
+      <c r="D446" t="s">
+        <v>204</v>
+      </c>
+      <c r="E446">
+        <v>1</v>
+      </c>
+      <c r="G446" t="s">
+        <v>743</v>
+      </c>
+      <c r="H446" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447" t="s">
+        <v>363</v>
+      </c>
+      <c r="C447">
+        <v>235</v>
+      </c>
+      <c r="D447" t="s">
+        <v>211</v>
+      </c>
+      <c r="E447">
+        <v>1</v>
+      </c>
+      <c r="G447" t="s">
+        <v>743</v>
+      </c>
+      <c r="H447" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448" t="s">
+        <v>363</v>
+      </c>
+      <c r="C448">
+        <v>200</v>
+      </c>
+      <c r="D448" t="s">
+        <v>215</v>
+      </c>
+      <c r="E448">
+        <v>1</v>
+      </c>
+      <c r="G448" t="s">
+        <v>743</v>
+      </c>
+      <c r="H448" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449" t="s">
+        <v>363</v>
+      </c>
+      <c r="C449">
+        <v>201</v>
+      </c>
+      <c r="D449" t="s">
+        <v>169</v>
+      </c>
+      <c r="E449">
+        <v>1</v>
+      </c>
+      <c r="G449" t="s">
+        <v>743</v>
+      </c>
+      <c r="H449" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450" t="s">
+        <v>363</v>
+      </c>
+      <c r="C450">
+        <v>202</v>
+      </c>
+      <c r="D450" t="s">
+        <v>174</v>
+      </c>
+      <c r="E450">
+        <v>1</v>
+      </c>
+      <c r="G450" t="s">
+        <v>743</v>
+      </c>
+      <c r="H450" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451" t="s">
+        <v>375</v>
+      </c>
+      <c r="C451">
+        <v>230</v>
+      </c>
+      <c r="D451" t="s">
+        <v>188</v>
+      </c>
+      <c r="E451">
+        <v>1</v>
+      </c>
+      <c r="F451">
+        <v>441</v>
+      </c>
+      <c r="G451" t="s">
+        <v>753</v>
+      </c>
+      <c r="H451" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452" t="s">
+        <v>368</v>
+      </c>
+      <c r="C452">
+        <v>231</v>
+      </c>
+      <c r="D452" t="s">
+        <v>192</v>
+      </c>
+      <c r="E452">
+        <v>1</v>
+      </c>
+      <c r="F452">
+        <v>442</v>
+      </c>
+      <c r="G452" t="s">
+        <v>755</v>
+      </c>
+      <c r="H452" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453" t="s">
+        <v>368</v>
+      </c>
+      <c r="C453">
+        <v>232</v>
+      </c>
+      <c r="D453" t="s">
+        <v>196</v>
+      </c>
+      <c r="E453">
+        <v>1</v>
+      </c>
+      <c r="F453">
+        <v>443</v>
+      </c>
+      <c r="G453" t="s">
+        <v>755</v>
+      </c>
+      <c r="H453" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454" t="s">
+        <v>368</v>
+      </c>
+      <c r="C454">
+        <v>233</v>
+      </c>
+      <c r="D454" t="s">
+        <v>200</v>
+      </c>
+      <c r="E454">
+        <v>1</v>
+      </c>
+      <c r="F454">
+        <v>444</v>
+      </c>
+      <c r="G454" t="s">
+        <v>755</v>
+      </c>
+      <c r="H454" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455" t="s">
+        <v>368</v>
+      </c>
+      <c r="C455">
+        <v>234</v>
+      </c>
+      <c r="D455" t="s">
+        <v>204</v>
+      </c>
+      <c r="E455">
+        <v>1</v>
+      </c>
+      <c r="F455">
+        <v>445</v>
+      </c>
+      <c r="G455" t="s">
+        <v>755</v>
+      </c>
+      <c r="H455" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456" t="s">
+        <v>368</v>
+      </c>
+      <c r="C456">
+        <v>235</v>
+      </c>
+      <c r="D456" t="s">
+        <v>211</v>
+      </c>
+      <c r="E456">
+        <v>1</v>
+      </c>
+      <c r="F456">
+        <v>446</v>
+      </c>
+      <c r="G456" t="s">
+        <v>755</v>
+      </c>
+      <c r="H456" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457" t="s">
+        <v>368</v>
+      </c>
+      <c r="C457">
+        <v>200</v>
+      </c>
+      <c r="D457" t="s">
+        <v>215</v>
+      </c>
+      <c r="E457">
+        <v>1</v>
+      </c>
+      <c r="F457">
+        <v>447</v>
+      </c>
+      <c r="G457" t="s">
+        <v>755</v>
+      </c>
+      <c r="H457" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458" t="s">
+        <v>368</v>
+      </c>
+      <c r="C458">
+        <v>201</v>
+      </c>
+      <c r="D458" t="s">
+        <v>169</v>
+      </c>
+      <c r="E458">
+        <v>1</v>
+      </c>
+      <c r="F458">
+        <v>448</v>
+      </c>
+      <c r="G458" t="s">
+        <v>755</v>
+      </c>
+      <c r="H458" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459" t="s">
+        <v>224</v>
+      </c>
+      <c r="C459">
+        <v>114</v>
+      </c>
+      <c r="E459">
+        <v>24</v>
+      </c>
+      <c r="G459" t="s">
+        <v>763</v>
+      </c>
+      <c r="H459" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460" t="s">
+        <v>224</v>
+      </c>
+      <c r="C460">
+        <v>122</v>
+      </c>
+      <c r="E460">
+        <v>24</v>
+      </c>
+      <c r="G460" t="s">
+        <v>763</v>
+      </c>
+      <c r="H460" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>300</v>
+      </c>
+      <c r="C461">
+        <v>131</v>
+      </c>
+      <c r="E461">
+        <v>24</v>
+      </c>
+      <c r="G461" t="s">
+        <v>766</v>
+      </c>
+      <c r="H461" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" t="s">
+        <v>300</v>
+      </c>
+      <c r="C462">
+        <v>132</v>
+      </c>
+      <c r="E462">
+        <v>4</v>
+      </c>
+      <c r="G462" t="s">
+        <v>766</v>
+      </c>
+      <c r="H462" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" t="s">
+        <v>300</v>
+      </c>
+      <c r="C463">
+        <v>133</v>
+      </c>
+      <c r="E463">
+        <v>6</v>
+      </c>
+      <c r="G463" t="s">
+        <v>766</v>
+      </c>
+      <c r="H463" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" t="s">
+        <v>300</v>
+      </c>
+      <c r="C464">
+        <v>135</v>
+      </c>
+      <c r="E464">
+        <v>24</v>
+      </c>
+      <c r="G464" t="s">
+        <v>766</v>
+      </c>
+      <c r="H464" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465" t="s">
+        <v>300</v>
+      </c>
+      <c r="C465">
+        <v>100</v>
+      </c>
+      <c r="E465">
+        <v>4</v>
+      </c>
+      <c r="G465" t="s">
+        <v>766</v>
+      </c>
+      <c r="H465" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466" t="s">
+        <v>300</v>
+      </c>
+      <c r="C466">
+        <v>101</v>
+      </c>
+      <c r="E466">
+        <v>6</v>
+      </c>
+      <c r="G466" t="s">
+        <v>766</v>
+      </c>
+      <c r="H466" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467" t="s">
+        <v>300</v>
+      </c>
+      <c r="C467">
+        <v>102</v>
+      </c>
+      <c r="E467">
+        <v>12</v>
+      </c>
+      <c r="G467" t="s">
+        <v>766</v>
+      </c>
+      <c r="H467" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468" t="s">
+        <v>300</v>
+      </c>
+      <c r="C468">
+        <v>103</v>
+      </c>
+      <c r="E468">
+        <v>24</v>
+      </c>
+      <c r="G468" t="s">
+        <v>766</v>
+      </c>
+      <c r="H468" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469" t="s">
+        <v>300</v>
+      </c>
+      <c r="C469">
+        <v>104</v>
+      </c>
+      <c r="E469">
+        <v>5</v>
+      </c>
+      <c r="G469" t="s">
+        <v>766</v>
+      </c>
+      <c r="H469" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470" t="s">
+        <v>300</v>
+      </c>
+      <c r="C470">
+        <v>105</v>
+      </c>
+      <c r="E470">
+        <v>6</v>
+      </c>
+      <c r="G470" t="s">
+        <v>766</v>
+      </c>
+      <c r="H470" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471" t="s">
+        <v>300</v>
+      </c>
+      <c r="C471">
+        <v>106</v>
+      </c>
+      <c r="E471">
+        <v>12</v>
+      </c>
+      <c r="G471" t="s">
+        <v>766</v>
+      </c>
+      <c r="H471" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472" t="s">
+        <v>300</v>
+      </c>
+      <c r="C472">
+        <v>107</v>
+      </c>
+      <c r="E472">
+        <v>24</v>
+      </c>
+      <c r="G472" t="s">
+        <v>766</v>
+      </c>
+      <c r="H472" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473" t="s">
+        <v>300</v>
+      </c>
+      <c r="C473">
+        <v>108</v>
+      </c>
+      <c r="E473">
+        <v>3</v>
+      </c>
+      <c r="G473" t="s">
+        <v>766</v>
+      </c>
+      <c r="H473" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474" t="s">
+        <v>300</v>
+      </c>
+      <c r="C474">
+        <v>109</v>
+      </c>
+      <c r="E474">
+        <v>6</v>
+      </c>
+      <c r="G474" t="s">
+        <v>766</v>
+      </c>
+      <c r="H474" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475" t="s">
+        <v>363</v>
+      </c>
+      <c r="C475">
+        <v>203</v>
+      </c>
+      <c r="D475" t="s">
+        <v>192</v>
+      </c>
+      <c r="E475">
+        <v>1</v>
+      </c>
+      <c r="G475" t="s">
+        <v>781</v>
+      </c>
+      <c r="H475" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476" t="s">
+        <v>363</v>
+      </c>
+      <c r="C476">
+        <v>204</v>
+      </c>
+      <c r="D476" t="s">
+        <v>196</v>
+      </c>
+      <c r="E476">
+        <v>1</v>
+      </c>
+      <c r="G476" t="s">
+        <v>781</v>
+      </c>
+      <c r="H476" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477" t="s">
+        <v>363</v>
+      </c>
+      <c r="C477">
+        <v>205</v>
+      </c>
+      <c r="D477" t="s">
+        <v>200</v>
+      </c>
+      <c r="E477">
+        <v>1</v>
+      </c>
+      <c r="G477" t="s">
+        <v>781</v>
+      </c>
+      <c r="H477" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478" t="s">
+        <v>363</v>
+      </c>
+      <c r="C478">
+        <v>206</v>
+      </c>
+      <c r="D478" t="s">
+        <v>204</v>
+      </c>
+      <c r="E478">
+        <v>1</v>
+      </c>
+      <c r="G478" t="s">
+        <v>781</v>
+      </c>
+      <c r="H478" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479" t="s">
+        <v>363</v>
+      </c>
+      <c r="C479">
+        <v>208</v>
+      </c>
+      <c r="D479" t="s">
+        <v>211</v>
+      </c>
+      <c r="E479">
+        <v>1</v>
+      </c>
+      <c r="G479" t="s">
+        <v>781</v>
+      </c>
+      <c r="H479" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480" t="s">
+        <v>363</v>
+      </c>
+      <c r="C480">
+        <v>210</v>
+      </c>
+      <c r="D480" t="s">
+        <v>215</v>
+      </c>
+      <c r="E480">
+        <v>1</v>
+      </c>
+      <c r="G480" t="s">
+        <v>781</v>
+      </c>
+      <c r="H480" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481" t="s">
+        <v>363</v>
+      </c>
+      <c r="C481">
+        <v>212</v>
+      </c>
+      <c r="D481" t="s">
+        <v>169</v>
+      </c>
+      <c r="E481">
+        <v>1</v>
+      </c>
+      <c r="G481" t="s">
+        <v>781</v>
+      </c>
+      <c r="H481" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482" t="s">
+        <v>363</v>
+      </c>
+      <c r="C482">
+        <v>213</v>
+      </c>
+      <c r="D482" t="s">
+        <v>174</v>
+      </c>
+      <c r="E482">
+        <v>1</v>
+      </c>
+      <c r="G482" t="s">
+        <v>781</v>
+      </c>
+      <c r="H482" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483" t="s">
+        <v>363</v>
+      </c>
+      <c r="C483">
+        <v>214</v>
+      </c>
+      <c r="D483" t="s">
+        <v>183</v>
+      </c>
+      <c r="E483">
+        <v>1</v>
+      </c>
+      <c r="G483" t="s">
+        <v>781</v>
+      </c>
+      <c r="H483" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>483</v>
+      </c>
+      <c r="B484" t="s">
+        <v>307</v>
+      </c>
+      <c r="C484">
+        <v>218</v>
+      </c>
+      <c r="E484">
+        <v>1</v>
+      </c>
+      <c r="G484" t="s">
+        <v>559</v>
+      </c>
+      <c r="H484" t="s">
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -11136,13 +17825,13 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>792</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>495</v>
+        <v>793</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11226,7 +17915,7 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -11252,22 +17941,22 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>792</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>496</v>
+        <v>794</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>497</v>
+        <v>795</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>498</v>
+        <v>796</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>499</v>
+        <v>797</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -11284,13 +17973,13 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -11310,10 +17999,10 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -11330,13 +18019,13 @@
         <v>140</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -11356,10 +18045,10 @@
         <v>15</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="G5">
-        <v>150</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -11376,13 +18065,13 @@
         <v>180</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -11402,10 +18091,10 @@
         <v>40</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -11422,13 +18111,13 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -11445,13 +18134,13 @@
         <v>140</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G9">
-        <v>165</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -11468,13 +18157,13 @@
         <v>160</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -11491,13 +18180,13 @@
         <v>180</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G11">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -11514,13 +18203,13 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -11537,13 +18226,13 @@
         <v>120</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G13">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -11560,13 +18249,13 @@
         <v>140</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -11583,13 +18272,13 @@
         <v>160</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G15">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -11606,13 +18295,13 @@
         <v>180</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G16">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -11629,13 +18318,13 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="G17">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -11655,10 +18344,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -11698,13 +18387,13 @@
         <v>160</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G20">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -11724,10 +18413,10 @@
         <v>25</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G21">
-        <v>205</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -11744,13 +18433,13 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G22">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -11770,10 +18459,10 @@
         <v>15</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G23">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -11790,13 +18479,13 @@
         <v>140</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G24">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -11816,10 +18505,10 @@
         <v>40</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G25">
-        <v>182</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,10 +18528,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -11862,10 +18551,10 @@
         <v>25</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G27">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -11885,10 +18574,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G28">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -11908,10 +18597,10 @@
         <v>15</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="G29">
-        <v>130</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -11931,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -11954,10 +18643,10 @@
         <v>40</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G31">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -11977,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -12000,10 +18689,10 @@
         <v>25</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G33">
-        <v>145</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -12023,10 +18712,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -12046,10 +18735,10 @@
         <v>15</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G35">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -12092,10 +18781,10 @@
         <v>40</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G37">
-        <v>122</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -12,13 +12,15 @@
     <sheet sheetId="6" name="Recovery Events" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Unresolved Damage" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Consumables Usage" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Recovery Radio Fleet" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Recovery Radios" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="803">
   <si>
     <t>Name</t>
   </si>
@@ -2412,6 +2414,21 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Holder</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Lost</t>
   </si>
 </sst>
 </file>
@@ -2837,6 +2854,31 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H73"/>
@@ -18792,4 +18834,25 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="814">
   <si>
     <t>Name</t>
   </si>
@@ -2449,6 +2449,21 @@
   </si>
   <si>
     <t>Outstanding</t>
+  </si>
+  <si>
+    <t>Next Item Code</t>
+  </si>
+  <si>
+    <t>Next Item ID</t>
+  </si>
+  <si>
+    <t>Next Borrower ID</t>
+  </si>
+  <si>
+    <t>Next Location ID</t>
+  </si>
+  <si>
+    <t>Next Event ID</t>
   </si>
 </sst>
 </file>
@@ -5413,28 +5428,58 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D1" t="s">
+        <v>811</v>
+      </c>
+      <c r="E1" t="s">
+        <v>812</v>
+      </c>
+      <c r="F1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>483</v>
       </c>
+      <c r="B2">
+        <v>236</v>
+      </c>
+      <c r="C2">
+        <v>73</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>484</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="824">
   <si>
     <t>Name</t>
   </si>
@@ -2443,6 +2443,36 @@
   </si>
   <si>
     <t>Team</t>
+  </si>
+  <si>
+    <t>מתנדב מד״א</t>
+  </si>
+  <si>
+    <t>מד״א</t>
+  </si>
+  <si>
+    <t>צוות הפקה</t>
+  </si>
+  <si>
+    <t>במה</t>
+  </si>
+  <si>
+    <t>מאנקי</t>
+  </si>
+  <si>
+    <t>לוגיסטיקה</t>
+  </si>
+  <si>
+    <t>נועה כהן</t>
+  </si>
+  <si>
+    <t>רפואה</t>
+  </si>
+  <si>
+    <t>עובד מד״א</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Checkout ID</t>
@@ -2891,7 +2921,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2906,6 +2936,216 @@
       </c>
       <c r="D1" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C4" t="s">
+        <v>812</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>813</v>
+      </c>
+      <c r="C5" t="s">
+        <v>814</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>815</v>
+      </c>
+      <c r="C6" t="s">
+        <v>808</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>816</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>816</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>816</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>816</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>816</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>816</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>816</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>816</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>816</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2921,7 +3161,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -2936,7 +3176,7 @@
         <v>107</v>
       </c>
       <c r="F1" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="G1" t="s">
         <v>113</v>
@@ -5442,19 +5682,19 @@
         <v>114</v>
       </c>
       <c r="B1" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="C1" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="D1" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="E1" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="F1" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -22547,7 +22787,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -2921,7 +2921,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3145,6 +3145,356 @@
         <v>816</v>
       </c>
       <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C17" t="str"/>
+      <c r="D17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C18" t="str"/>
+      <c r="D18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C19" t="str"/>
+      <c r="D19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C20" t="str"/>
+      <c r="D20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C21" t="str"/>
+      <c r="D21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C22" t="str"/>
+      <c r="D22" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C23" t="str"/>
+      <c r="D23" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C24" t="str"/>
+      <c r="D24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C25" t="str"/>
+      <c r="D25" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C26" t="str"/>
+      <c r="D26" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C27" t="str"/>
+      <c r="D27" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C28" t="str"/>
+      <c r="D28" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C29" t="str"/>
+      <c r="D29" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C30" t="str"/>
+      <c r="D30" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C31" t="str"/>
+      <c r="D31" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C32" t="str"/>
+      <c r="D32" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C33" t="str"/>
+      <c r="D33" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C34" t="str"/>
+      <c r="D34" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C35" t="str"/>
+      <c r="D35" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C36" t="str"/>
+      <c r="D36" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C37" t="str"/>
+      <c r="D37" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C38" t="str"/>
+      <c r="D38" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C39" t="str"/>
+      <c r="D39" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C40" t="str"/>
+      <c r="D40" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>צוללת</t>
+        </is>
+      </c>
+      <c r="C41" t="str"/>
+      <c r="D41" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22787,7 +23137,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="823">
   <si>
     <t>Name</t>
   </si>
@@ -39,9 +39,6 @@
     <t>צוללת</t>
   </si>
   <si>
-    <t>Item Code</t>
-  </si>
-  <si>
     <t>Kind</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
     <t>גלגלות חשמל</t>
   </si>
   <si>
+    <t>Item ID</t>
+  </si>
+  <si>
     <t>Created At</t>
   </si>
   <si>
@@ -2479,9 +2479,6 @@
   </si>
   <si>
     <t>Outstanding</t>
-  </si>
-  <si>
-    <t>Next Item Code</t>
   </si>
   <si>
     <t>Next Item ID</t>
@@ -3148,357 +3145,283 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C17" t="str"/>
-      <c r="D17" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C18" t="str"/>
-      <c r="D18" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C19" t="str"/>
-      <c r="D19" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C20" t="str"/>
-      <c r="D20" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C21" t="str"/>
-      <c r="D21" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C22" t="str"/>
-      <c r="D22" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C23" t="str"/>
-      <c r="D23" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C24" t="str"/>
-      <c r="D24" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C25" t="str"/>
-      <c r="D25" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C26" t="str"/>
-      <c r="D26" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C27" t="str"/>
-      <c r="D27" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C28" t="str"/>
-      <c r="D28" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C29" t="str"/>
-      <c r="D29" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C30" t="str"/>
-      <c r="D30" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C31" t="str"/>
-      <c r="D31" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C32" t="str"/>
-      <c r="D32" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C33" t="str"/>
-      <c r="D33" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C34" t="str"/>
-      <c r="D34" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C35" t="str"/>
-      <c r="D35" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C36" t="str"/>
-      <c r="D36" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C37" t="str"/>
-      <c r="D37" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C38" t="str"/>
-      <c r="D38" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C39" t="str"/>
-      <c r="D39" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C40" t="str"/>
-      <c r="D40" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>צוללת</t>
-        </is>
-      </c>
-      <c r="C41" t="str"/>
-      <c r="D41" s="2" t="b">
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -3514,7 +3437,7 @@
         <v>817</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
         <v>225</v>
@@ -6017,6 +5940,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -6024,10 +5948,10 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>114</v>
       </c>
@@ -6043,31 +5967,26 @@
       <c r="E1" t="s">
         <v>822</v>
       </c>
-      <c r="F1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>483</v>
       </c>
       <c r="B2">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="C2">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
         <v>484</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -6075,18 +5994,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="8" width="12" customWidth="1"/>
+    <col min="1" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
@@ -6098,1754 +6017,1535 @@
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>24</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>24</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15">
         <v>6</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>24</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
         <v>4</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4">
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20">
         <v>12</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>103</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>24</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25">
+        <v>24</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5">
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28">
+        <v>12</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29">
         <v>24</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>12</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33">
+        <v>24</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>106</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>107</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9">
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37">
         <v>24</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>111</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13">
-        <v>24</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16">
-        <v>12</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17">
-        <v>24</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>116</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>117</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19">
-        <v>6</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>118</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20">
-        <v>12</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>119</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21">
-        <v>24</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>120</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>121</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23">
-        <v>6</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24">
-        <v>12</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>124</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>125</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27">
-        <v>6</v>
-      </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>126</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28">
-        <v>12</v>
-      </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>127</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29">
-        <v>24</v>
-      </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>129</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>50</v>
       </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31">
-        <v>6</v>
-      </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>130</v>
-      </c>
-      <c r="B32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32">
-        <v>12</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>131</v>
-      </c>
-      <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33">
-        <v>24</v>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>132</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>133</v>
-      </c>
-      <c r="B35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35">
-        <v>6</v>
-      </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>134</v>
-      </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36">
-        <v>12</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>135</v>
-      </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>57</v>
-      </c>
-      <c r="C37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37">
-        <v>24</v>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>200</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
       <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
         <v>59</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
         <v>4</v>
       </c>
-      <c r="E38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>201</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>61</v>
       </c>
-      <c r="C39" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
         <v>4</v>
       </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39">
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>202</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
         <v>4</v>
       </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40">
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>203</v>
-      </c>
-      <c r="B41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
         <v>4</v>
       </c>
-      <c r="E41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41">
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>204</v>
-      </c>
-      <c r="B42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" t="s">
         <v>4</v>
       </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="D56" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>87</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>205</v>
-      </c>
-      <c r="B43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" t="s">
-        <v>59</v>
-      </c>
-      <c r="D43" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
         <v>4</v>
       </c>
-      <c r="E43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43">
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>206</v>
-      </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="s">
-        <v>59</v>
-      </c>
-      <c r="D44" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" t="s">
         <v>4</v>
       </c>
-      <c r="E44" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44">
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
+      <c r="G65">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>207</v>
-      </c>
-      <c r="B45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" t="s">
         <v>4</v>
       </c>
-      <c r="E45" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>208</v>
-      </c>
-      <c r="B46" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
         <v>4</v>
       </c>
-      <c r="E46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46">
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>209</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" t="s">
         <v>4</v>
       </c>
-      <c r="E47" t="s">
-        <v>72</v>
-      </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>210</v>
-      </c>
-      <c r="B48" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="D68" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" t="s">
         <v>3</v>
       </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>211</v>
-      </c>
-      <c r="B49" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>212</v>
-      </c>
-      <c r="B50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" t="s">
-        <v>4</v>
-      </c>
-      <c r="E50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50">
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>103</v>
+      </c>
+      <c r="F71" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>213</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>214</v>
-      </c>
-      <c r="B52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73">
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>215</v>
-      </c>
-      <c r="B53" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" t="s">
-        <v>80</v>
-      </c>
-      <c r="G53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>216</v>
-      </c>
-      <c r="B54" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>217</v>
-      </c>
-      <c r="B55" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>218</v>
-      </c>
-      <c r="B56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" t="s">
-        <v>84</v>
-      </c>
-      <c r="G56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>219</v>
-      </c>
-      <c r="B57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>220</v>
-      </c>
-      <c r="B58" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>221</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" t="s">
-        <v>88</v>
-      </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>222</v>
-      </c>
-      <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>223</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" t="s">
-        <v>4</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>224</v>
-      </c>
-      <c r="B62" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" t="s">
-        <v>92</v>
-      </c>
-      <c r="G62" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>225</v>
-      </c>
-      <c r="B63" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" t="s">
-        <v>4</v>
-      </c>
-      <c r="E63" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>226</v>
-      </c>
-      <c r="B64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>227</v>
-      </c>
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>59</v>
-      </c>
-      <c r="D65" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" t="s">
-        <v>96</v>
-      </c>
-      <c r="G65" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>228</v>
-      </c>
-      <c r="B66" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
-      </c>
-      <c r="D66" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>229</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" t="s">
-        <v>59</v>
-      </c>
-      <c r="D67" t="s">
-        <v>4</v>
-      </c>
-      <c r="E67" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>230</v>
-      </c>
-      <c r="B68" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" t="s">
-        <v>4</v>
-      </c>
-      <c r="E68" t="s">
-        <v>100</v>
-      </c>
-      <c r="G68" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>231</v>
-      </c>
-      <c r="B69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C69" t="s">
-        <v>59</v>
-      </c>
-      <c r="D69" t="s">
-        <v>4</v>
-      </c>
-      <c r="E69" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" t="b">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>232</v>
-      </c>
-      <c r="B70" t="s">
-        <v>102</v>
-      </c>
-      <c r="C70" t="s">
-        <v>59</v>
-      </c>
-      <c r="D70" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" t="b">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>233</v>
-      </c>
-      <c r="B71" t="s">
-        <v>103</v>
-      </c>
-      <c r="C71" t="s">
-        <v>59</v>
-      </c>
-      <c r="D71" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" t="s">
-        <v>104</v>
-      </c>
-      <c r="G71" t="b">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>234</v>
-      </c>
-      <c r="B72" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" t="s">
-        <v>59</v>
-      </c>
-      <c r="D72" t="s">
-        <v>2</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" t="b">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>235</v>
-      </c>
-      <c r="B73" t="s">
-        <v>106</v>
-      </c>
-      <c r="C73" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" t="s">
-        <v>2</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" t="b">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -7910,22 +7610,22 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -7960,16 +7660,16 @@
         <v>100</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -8004,16 +7704,16 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -8051,16 +7751,16 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -8098,16 +7798,16 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>24</v>
@@ -8145,16 +7845,16 @@
         <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -8189,16 +7889,16 @@
         <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -8236,16 +7936,16 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -8283,16 +7983,16 @@
         <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9">
         <v>24</v>
@@ -8330,16 +8030,16 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8374,16 +8074,16 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -8421,16 +8121,16 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12">
         <v>12</v>
@@ -8468,16 +8168,16 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13">
         <v>24</v>
@@ -8515,16 +8215,16 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -8559,16 +8259,16 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -8606,16 +8306,16 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -8653,16 +8353,16 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17">
         <v>24</v>
@@ -8700,16 +8400,16 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -8744,16 +8444,16 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -8791,16 +8491,16 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -8838,16 +8538,16 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>24</v>
@@ -8885,16 +8585,16 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -8929,16 +8629,16 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23">
         <v>6</v>
@@ -8976,16 +8676,16 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24">
         <v>12</v>
@@ -9023,16 +8723,16 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -9070,16 +8770,16 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -9114,16 +8814,16 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -9161,16 +8861,16 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28">
         <v>12</v>
@@ -9208,16 +8908,16 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29">
         <v>24</v>
@@ -9255,16 +8955,16 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -9299,16 +8999,16 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -9346,16 +9046,16 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F32">
         <v>12</v>
@@ -9393,16 +9093,16 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F33">
         <v>24</v>
@@ -9440,16 +9140,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D34" t="s">
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -9484,16 +9184,16 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F35">
         <v>6</v>
@@ -9531,16 +9231,16 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F36">
         <v>12</v>
@@ -9578,16 +9278,16 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" t="s">
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F37">
         <v>24</v>
@@ -9625,16 +9325,16 @@
         <v>200</v>
       </c>
       <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
         <v>58</v>
-      </c>
-      <c r="C38" t="s">
-        <v>59</v>
       </c>
       <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -9669,16 +9369,16 @@
         <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -9713,16 +9413,16 @@
         <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -9757,16 +9457,16 @@
         <v>203</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -9801,16 +9501,16 @@
         <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -9845,16 +9545,16 @@
         <v>205</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -9889,16 +9589,16 @@
         <v>206</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -9933,16 +9633,16 @@
         <v>207</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -9977,16 +9677,16 @@
         <v>208</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -10021,16 +9721,16 @@
         <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -10065,16 +9765,16 @@
         <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -10109,16 +9809,16 @@
         <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -10153,16 +9853,16 @@
         <v>212</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -10197,16 +9897,16 @@
         <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
@@ -10241,16 +9941,16 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -10285,16 +9985,16 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
@@ -10329,16 +10029,16 @@
         <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -10373,16 +10073,16 @@
         <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -10417,16 +10117,16 @@
         <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
@@ -10461,16 +10161,16 @@
         <v>219</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -10505,16 +10205,16 @@
         <v>220</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
@@ -10549,16 +10249,16 @@
         <v>221</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -10593,16 +10293,16 @@
         <v>222</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -10637,16 +10337,16 @@
         <v>223</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
@@ -10681,16 +10381,16 @@
         <v>224</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -10725,16 +10425,16 @@
         <v>225</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -10769,16 +10469,16 @@
         <v>226</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
@@ -10813,16 +10513,16 @@
         <v>227</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
         <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
@@ -10857,16 +10557,16 @@
         <v>228</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
         <v>4</v>
       </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -10901,16 +10601,16 @@
         <v>229</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
         <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
@@ -10945,16 +10645,16 @@
         <v>230</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D68" t="s">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -10989,16 +10689,16 @@
         <v>231</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
@@ -11033,16 +10733,16 @@
         <v>232</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G70" t="b">
         <v>0</v>
@@ -11077,16 +10777,16 @@
         <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D71" t="s">
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
@@ -11121,16 +10821,16 @@
         <v>234</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D72" t="s">
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -11165,16 +10865,16 @@
         <v>235</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
         <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -11205,7 +10905,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -11506,10 +11206,10 @@
         <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>225</v>
@@ -22144,113 +21844,92 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>797</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>797</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>203</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>206</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>215</v>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>218</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>227</v>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>230</v>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -22258,868 +21937,757 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>797</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>797</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>799</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
         <v>100</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>120</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>140</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>78</v>
+      </c>
+      <c r="F4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>160</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>116</v>
+      </c>
+      <c r="F5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>180</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>39</v>
+      </c>
+      <c r="F7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>120</v>
+      </c>
+      <c r="D8">
+        <v>24</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>140</v>
+      </c>
+      <c r="D9">
+        <v>73</v>
+      </c>
+      <c r="E9">
+        <v>96</v>
+      </c>
+      <c r="F9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>160</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>44</v>
+      </c>
+      <c r="F10">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>180</v>
+      </c>
+      <c r="D11">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>36</v>
+      </c>
+      <c r="F12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>120</v>
+      </c>
+      <c r="D13">
+        <v>88</v>
+      </c>
+      <c r="E13">
+        <v>87</v>
+      </c>
+      <c r="F13">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>140</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="D2">
+      <c r="C15">
+        <v>160</v>
+      </c>
+      <c r="D15">
+        <v>37</v>
+      </c>
+      <c r="E15">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>180</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>66</v>
+      </c>
+      <c r="F16">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="D17">
+        <v>63</v>
+      </c>
+      <c r="E17">
+        <v>92</v>
+      </c>
+      <c r="F17">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>120</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>140</v>
+      </c>
+      <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>160</v>
+      </c>
+      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>36</v>
+      </c>
+      <c r="F20">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>180</v>
+      </c>
+      <c r="D21">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <v>72</v>
+      </c>
+      <c r="F21">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
         <v>30</v>
       </c>
-      <c r="F2">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E22">
+        <v>43</v>
+      </c>
+      <c r="F22">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>120</v>
+      </c>
+      <c r="D23">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>38</v>
+      </c>
+      <c r="F23">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>140</v>
+      </c>
+      <c r="D24">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>36</v>
+      </c>
+      <c r="F24">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>160</v>
+      </c>
+      <c r="D25">
+        <v>40</v>
+      </c>
+      <c r="E25">
+        <v>87</v>
+      </c>
+      <c r="F25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>180</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27">
+        <v>18</v>
+      </c>
+      <c r="F27">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>120</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>66</v>
+      </c>
+      <c r="F28">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>140</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>92</v>
+      </c>
+      <c r="F29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>160</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F30">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="C31">
+        <v>180</v>
+      </c>
+      <c r="D31">
+        <v>40</v>
+      </c>
+      <c r="E31">
+        <v>33</v>
+      </c>
+      <c r="F31">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>36</v>
+      </c>
+      <c r="F32">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33">
         <v>120</v>
       </c>
-      <c r="E3">
+      <c r="D33">
         <v>25</v>
       </c>
-      <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+      <c r="E33">
+        <v>72</v>
+      </c>
+      <c r="F33">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34">
         <v>140</v>
       </c>
-      <c r="E4">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>78</v>
-      </c>
-      <c r="G4">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>103</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>40</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35">
         <v>160</v>
       </c>
-      <c r="E5">
+      <c r="D35">
         <v>15</v>
       </c>
-      <c r="F5">
-        <v>116</v>
-      </c>
-      <c r="G5">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6">
+      <c r="E35">
+        <v>38</v>
+      </c>
+      <c r="F35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36">
         <v>180</v>
       </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7">
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37">
         <v>100</v>
       </c>
-      <c r="E7">
+      <c r="D37">
         <v>40</v>
       </c>
-      <c r="F7">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>106</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>120</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>107</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>140</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>96</v>
-      </c>
-      <c r="G9">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>160</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>44</v>
-      </c>
-      <c r="G10">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>180</v>
-      </c>
-      <c r="E11">
-        <v>27</v>
-      </c>
-      <c r="F11">
-        <v>44</v>
-      </c>
-      <c r="G11">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>24</v>
-      </c>
-      <c r="F12">
-        <v>36</v>
-      </c>
-      <c r="G12">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>111</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>120</v>
-      </c>
-      <c r="E13">
-        <v>88</v>
-      </c>
-      <c r="F13">
+      <c r="E37">
         <v>87</v>
       </c>
-      <c r="G13">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>140</v>
-      </c>
-      <c r="E14">
-        <v>30</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>160</v>
-      </c>
-      <c r="E15">
-        <v>37</v>
-      </c>
-      <c r="F15">
-        <v>18</v>
-      </c>
-      <c r="G15">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <v>180</v>
-      </c>
-      <c r="E16">
-        <v>24</v>
-      </c>
-      <c r="F16">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>63</v>
-      </c>
-      <c r="F17">
-        <v>92</v>
-      </c>
-      <c r="G17">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>116</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>120</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>117</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>140</v>
-      </c>
-      <c r="E19">
-        <v>40</v>
-      </c>
-      <c r="F19">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>118</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>160</v>
-      </c>
-      <c r="E20">
-        <v>24</v>
-      </c>
-      <c r="F20">
-        <v>36</v>
-      </c>
-      <c r="G20">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>119</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>180</v>
-      </c>
-      <c r="E21">
-        <v>25</v>
-      </c>
-      <c r="F21">
-        <v>72</v>
-      </c>
-      <c r="G21">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>120</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
-      <c r="E22">
-        <v>30</v>
-      </c>
-      <c r="F22">
-        <v>43</v>
-      </c>
-      <c r="G22">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>121</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>120</v>
-      </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
-      <c r="F23">
-        <v>38</v>
-      </c>
-      <c r="G23">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>140</v>
-      </c>
-      <c r="E24">
-        <v>24</v>
-      </c>
-      <c r="F24">
-        <v>36</v>
-      </c>
-      <c r="G24">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>160</v>
-      </c>
-      <c r="E25">
-        <v>40</v>
-      </c>
-      <c r="F25">
-        <v>87</v>
-      </c>
-      <c r="G25">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>124</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>180</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>125</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27">
-        <v>100</v>
-      </c>
-      <c r="E27">
-        <v>25</v>
-      </c>
-      <c r="F27">
-        <v>18</v>
-      </c>
-      <c r="G27">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>126</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>120</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>127</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>140</v>
-      </c>
-      <c r="E29">
-        <v>15</v>
-      </c>
-      <c r="F29">
-        <v>92</v>
-      </c>
-      <c r="G29">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>160</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>129</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="F37">
         <v>50</v>
       </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>180</v>
-      </c>
-      <c r="E31">
-        <v>40</v>
-      </c>
-      <c r="F31">
-        <v>33</v>
-      </c>
-      <c r="G31">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>130</v>
-      </c>
-      <c r="B32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32">
-        <v>100</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>36</v>
-      </c>
-      <c r="G32">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>131</v>
-      </c>
-      <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33">
-        <v>120</v>
-      </c>
-      <c r="E33">
-        <v>25</v>
-      </c>
-      <c r="F33">
-        <v>72</v>
-      </c>
-      <c r="G33">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>132</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>140</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>40</v>
-      </c>
-      <c r="G34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>133</v>
-      </c>
-      <c r="B35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>160</v>
-      </c>
-      <c r="E35">
-        <v>15</v>
-      </c>
-      <c r="F35">
-        <v>38</v>
-      </c>
-      <c r="G35">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>134</v>
-      </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>180</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>135</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>100</v>
-      </c>
-      <c r="E37">
-        <v>40</v>
-      </c>
-      <c r="F37">
-        <v>87</v>
-      </c>
-      <c r="G37">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -23141,6 +22709,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>

--- a/sample_data/mapatz-full-recovery-sample.xlsx
+++ b/sample_data/mapatz-full-recovery-sample.xlsx
@@ -4477,8 +4477,10 @@
       <c r="G2">
         <v>117</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>לסגור בסיום</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -4503,8 +4505,10 @@
       <c r="G3">
         <v>121</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>קופסה כחולה</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5455,8 +5459,10 @@
       <c r="G41">
         <v>6</v>
       </c>
-      <c r="H41" t="s">
-        <v>15</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ידית אדומה</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -5524,8 +5530,10 @@
       <c r="G44">
         <v>11</v>
       </c>
-      <c r="H44" t="s">
-        <v>15</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>להחזיר נקי</t>
+        </is>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6030,8 +6038,10 @@
       <c r="G66">
         <v>3</v>
       </c>
-      <c r="H66" t="s">
-        <v>15</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>לגלגל בסיום</t>
+        </is>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6076,8 +6086,10 @@
       <c r="G68">
         <v>8</v>
       </c>
-      <c r="H68" t="s">
-        <v>15</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>סט משותף</t>
+        </is>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -6260,8 +6272,10 @@
       <c r="G76">
         <v>3</v>
       </c>
-      <c r="H76" t="s">
-        <v>15</v>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ידית אדומה</t>
+        </is>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -6329,8 +6343,10 @@
       <c r="G79">
         <v>1</v>
       </c>
-      <c r="H79" t="s">
-        <v>15</v>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>להחזיר נקי</t>
+        </is>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -6651,8 +6667,10 @@
       <c r="G93">
         <v>3</v>
       </c>
-      <c r="H93" t="s">
-        <v>15</v>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>לגלגל בסיום</t>
+        </is>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -6871,8 +6889,10 @@
       <c r="O2">
         <v>485</v>
       </c>
-      <c r="P2" t="s">
-        <v>15</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>לסגור בסיום</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -6918,8 +6938,10 @@
       <c r="O3">
         <v>485</v>
       </c>
-      <c r="P3" t="s">
-        <v>15</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>לסגור בסיום</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -6968,8 +6990,10 @@
       <c r="O4">
         <v>487</v>
       </c>
-      <c r="P4" t="s">
-        <v>15</v>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>קופסה כחולה</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -7018,8 +7042,10 @@
       <c r="O5">
         <v>487</v>
       </c>
-      <c r="P5" t="s">
-        <v>15</v>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>קופסה כחולה</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -8882,8 +8908,10 @@
       <c r="O43">
         <v>489</v>
       </c>
-      <c r="P43" t="s">
-        <v>15</v>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ידית אדומה</t>
+        </is>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -8929,8 +8957,10 @@
       <c r="O44">
         <v>489</v>
       </c>
-      <c r="P44" t="s">
-        <v>15</v>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ידית אדומה</t>
+        </is>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -9117,8 +9147,10 @@
       <c r="O48">
         <v>493</v>
       </c>
-      <c r="P48" t="s">
-        <v>15</v>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>להחזיר נקי</t>
+        </is>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -9164,8 +9196,10 @@
       <c r="O49">
         <v>493</v>
       </c>
-      <c r="P49" t="s">
-        <v>15</v>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>להחזיר נקי</t>
+        </is>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -10198,8 +10232,10 @@
       <c r="O71">
         <v>423</v>
       </c>
-      <c r="P71" t="s">
-        <v>15</v>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>לגלגל בסיום</t>
+        </is>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
@@ -10292,8 +10328,10 @@
       <c r="O73">
         <v>497</v>
       </c>
-      <c r="P73" t="s">
-        <v>15</v>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>סט משותף</t>
+        </is>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
@@ -10339,8 +10377,10 @@
       <c r="O74">
         <v>497</v>
       </c>
-      <c r="P74" t="s">
-        <v>15</v>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>סט משותף</t>
+        </is>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
